--- a/content/Question Bank/Coding Questions/Unit 12 - Exception Handling/Unit 12 - Exception Handling - Coding Questions.xlsx
+++ b/content/Question Bank/Coding Questions/Unit 12 - Exception Handling/Unit 12 - Exception Handling - Coding Questions.xlsx
@@ -596,7 +596,8 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Read two whole numbers and print the first divided by the second using integer division. If the second number is zero, catch the error and print 'Cannot divide by zero'.
+          <t xml:space="preserve">
+After the semester party, Nikhil splits the total bill equally among his friends using a small program — but the one time he typed 0 friends by mistake, it crashed with an ugly error. Write a program that reads two whole numbers and prints the first divided by the second using integer division (//). If the second number is zero, catch the ZeroDivisionError and print 'Cannot divide by zero' instead of crashing.
 ### Input Format
 - Line 1: First number
 - Line 2: Second number
@@ -604,6 +605,8 @@
 ```
 5
 ```
+### Example Walkthrough
+Here the numbers are 10 and 2. Since 2 is not zero, no error is raised, and integer division 10 // 2 gives 5, so the program prints `5`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -752,7 +755,8 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Read a line of numbers and an index. Print the value at that index, or 'Index out of range' if the index is too large.
+          <t xml:space="preserve">
+Priya keeps her cricket team's over-by-over runs in a list and lets teammates ask for the runs in any over by its position. Sometimes someone asks for a position that doesn't exist, and the program crashes. Write a program that reads a line of numbers and then an index (a position, counting from 0). Print the value at that index; if the index is too large, catch the IndexError and print 'Index out of range'.
 ### Input Format
 - Line 1: Space-separated numbers
 - Line 2: An index
@@ -760,6 +764,8 @@
 ```
 20
 ```
+### Example Walkthrough
+The list is `10 20 30` and the index is 1. Counting from 0, position 1 holds the value 20, so no error occurs and the program prints `20`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -908,7 +914,8 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Read N key/value pairs and a key. Print the value for that key, or 'Key not found' if it is missing. Use a try/except on the dictionary lookup.
+          <t xml:space="preserve">
+The hostel office keeps a small lookup table: each line pairs a code (the key) with its value. When someone asks about a code that was never recorded, the program should answer politely instead of crashing. Write a program that reads N, then N 'key value' pairs into a dictionary, then one key. Using try/except around the dictionary lookup, print the value for that key, or 'Key not found' if it is missing.
 ### Input Format
 - Line 1: N
 - Next N lines: 'key value'
@@ -917,6 +924,8 @@
 ```
 1
 ```
+### Example Walkthrough
+The two pairs are `a 1` and `b 2`, and the key asked for is `a`. The lookup finds `a` in the dictionary without raising a KeyError, so the program prints its value, `1`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -1079,7 +1088,8 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Read two whole numbers and print the first divided by the second. If the second is zero, print 'Cannot divide'. Either way, print 'Done' at the end using a finally block.
+          <t xml:space="preserve">
+Sanya's physics lab program divides total distance by total time to compute speed, and the lab rules say every run must end with a 'Done' message in the record — whether the calculation worked or not. Write a program that reads two whole numbers and prints the first divided by the second; if the second is zero, print 'Cannot divide' instead. In both cases, print 'Done' at the end using a finally block, which always runs.
 ### Input Format
 - Line 1: First number
 - Line 2: Second number
@@ -1088,6 +1098,8 @@
 5.0
 Done
 ```
+### Example Walkthrough
+With 10 and 2, the division 10 / 2 succeeds and prints `5.0`. Then the finally block runs no matter what happened before, printing `Done` on the next line.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -1245,7 +1257,8 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Read two lines and divide the first by the second. Print 'Zero' if the second is zero and 'Invalid' if either value is not a number; otherwise print the result.
+          <t xml:space="preserve">
+A mobile recharge kiosk lets customers type two amounts to divide, but people type all sorts of things — sometimes a zero, sometimes words instead of numbers. Write a program that reads two lines and divides the first by the second. Print 'Zero' if the second value is zero (a ZeroDivisionError), 'Invalid' if either value is not a number (a ValueError), and otherwise print the result.
 ### Input Format
 - Line 1: First value
 - Line 2: Second value
@@ -1253,6 +1266,8 @@
 ```
 5.0
 ```
+### Example Walkthrough
+Both sample inputs, 10 and 2, convert to numbers without trouble, and 2 is not zero — so neither error occurs, and the program prints 10 / 2, which is `5.0`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -1403,13 +1418,16 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Read an age. Write code that raises a ValueError if the age is below 0 or above 150, then catch it and print 'Invalid age'. Otherwise print 'Valid age'.
+          <t xml:space="preserve">
+Volunteers signing people up for the college blood-donation camp must record a sensible age — typos like -5 or 200 have slipped through before. Write a program that reads an age and raises a ValueError yourself (using `raise`) if the age is below 0 or above 150. Catch that error and print 'Invalid age'; if no error is raised, print 'Valid age'.
 ### Input Format
 - Line 1: An age
 ### Output Format
 ```
 Valid age
 ```
+### Example Walkthrough
+The sample age is 25, which sits comfortably between 0 and 150. No ValueError is raised, the except block is skipped, and the program prints `Valid age`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -1552,7 +1570,8 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Read a value, then a minimum and maximum. Raise and catch a ValueError to print 'In range' if the value is between them (inclusive) and 'Out of range' otherwise.
+          <t xml:space="preserve">
+During internal exam moderation, every mark awarded must fall between a minimum and a maximum set by the department, and Ishan is writing the checker. Write a program that reads a value, then a line containing the minimum and maximum. Raise a ValueError when the value falls outside the range, catch it, and print 'Out of range'; if the value is between them (inclusive), print 'In range'.
 ### Input Format
 - Line 1: The value
 - Line 2: 'min max'
@@ -1560,6 +1579,8 @@
 ```
 In range
 ```
+### Example Walkthrough
+The value is 5 and the allowed range is 1 to 10. Since 1 &lt;= 5 &lt;= 10, no error is raised, so the program prints `In range`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -1710,7 +1731,8 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Define a custom InsufficientFunds exception. Read a starting balance and N operations ('deposit X' or 'withdraw X'); a withdrawal beyond the balance raises the exception. After each operation print the new balance, or 'Insufficient funds' if a withdrawal was refused.
+          <t xml:space="preserve">
+The campus canteen smart card works like a tiny bank: students deposit money and withdraw it to pay for meals, but the card must never go below zero. Write a program that defines a custom exception class named InsufficientFunds. Read a starting balance and N operations, each 'deposit X' or 'withdraw X'. A withdrawal larger than the current balance raises InsufficientFunds — catch it and print 'Insufficient funds' (the balance stays unchanged). After each successful operation, print the new balance.
 ### Input Format
 - Line 1: Starting balance
 - Line 2: N
@@ -1720,6 +1742,8 @@
 50
 Insufficient funds
 ```
+### Example Walkthrough
+Starting at 100, `withdraw 50` succeeds and the new balance `50` is printed. Then `withdraw 100` asks for more than the remaining 50, so InsufficientFunds is raised and the program prints `Insufficient funds`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -1886,7 +1910,8 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Read a name, an age, and an email. Validate in order: the name must not be empty, the age must be a whole number from 1 to 120, and the email must contain '@'. Print 'Valid' if all pass, otherwise print the first failure: 'Invalid name', 'Invalid age', or 'Invalid email'.
+          <t xml:space="preserve">
+Registrations for the inter-college hackathon are pouring in, and Anu must reject badly filled forms with a clear reason. Write a program that reads a name, an age, and an email, and checks them in order: the name must not be empty, the age must be a whole number from 1 to 120, and the email must contain '@'. Print 'Valid' if all three checks pass; otherwise print only the first failure: 'Invalid name', 'Invalid age', or 'Invalid email'.
 ### Input Format
 - Line 1: Name
 - Line 2: Age
@@ -1895,6 +1920,8 @@
 ```
 Valid
 ```
+### Example Walkthrough
+The sample form has the name `Asha` (not empty), the age 20 (a whole number between 1 and 120), and the email `asha@x.com` (contains '@'). All three checks pass, so the program prints `Valid`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -2061,7 +2088,8 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Read a number, an operator (+, -, *, or /), and a second number. Print the result, 'Cannot divide by zero' for division by zero, or 'Unknown operator' if the operator is not one of the four.
+          <t xml:space="preserve">
+Uncle Prakash's stationery shop runs a small calculator program at the billing counter, and it must never crash mid-billing no matter what gets typed. Write a program that reads a number, an operator (+, -, *, or /), and a second number, then prints the result of applying the operator. If the customer tries to divide by zero, print 'Cannot divide by zero'; if the operator is not one of the four, print 'Unknown operator'.
 ### Input Format
 - Line 1: First number
 - Line 2: Operator
@@ -2070,6 +2098,8 @@
 ```
 Cannot divide by zero
 ```
+### Example Walkthrough
+The sample inputs are 6, `/`, and 0. Dividing 6 by 0 raises a ZeroDivisionError, which the program catches instead of crashing, so it prints `Cannot divide by zero`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>

--- a/content/Question Bank/Coding Questions/Unit 12 - Exception Handling/Unit 12 - Exception Handling - Coding Questions.xlsx
+++ b/content/Question Bank/Coding Questions/Unit 12 - Exception Handling/Unit 12 - Exception Handling - Coding Questions.xlsx
@@ -1,13 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Set 1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Set 2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Set 3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Set 4" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH31"/>
+  <dimension ref="A1:AH11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -622,12 +625,22 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>python-fundamentals</t>
+          <t>python</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -781,12 +794,22 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>python-fundamentals</t>
+          <t>python</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -941,12 +964,22 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>python-fundamentals</t>
+          <t>python</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1115,12 +1148,22 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>python-fundamentals</t>
+          <t>python</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1283,12 +1326,22 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>python-fundamentals</t>
+          <t>python</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1298,7 +1351,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>try-except</t>
+          <t>exception-handling-patterns</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1443,12 +1496,22 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>python-fundamentals</t>
+          <t>python</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1458,7 +1521,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>raise-custom</t>
+          <t>raising-exceptions</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1596,12 +1659,22 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>python-fundamentals</t>
+          <t>python</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1611,7 +1684,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>validation</t>
+          <t>raising-exceptions</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1759,12 +1832,22 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>python-fundamentals</t>
+          <t>python</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1774,7 +1857,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>raise-custom</t>
+          <t>custom-exceptions</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1905,10 +1988,514 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Python - Safe Integer Input</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Safe Integer Input. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: Value
+### Output Format
+```
+10
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>exception-handling</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>try-except</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O10" t="b">
+        <v>0</v>
+      </c>
+      <c r="P10" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="b">
+        <v>1</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>abc</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Invalid</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>Invalid</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>Invalid</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>try:
+ print(int(input()))
+except ValueError: print("Invalid")</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Python - Safe List Index</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Safe List Index. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: Items
+- Line 2: Index
+### Output Format
+```
+b
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>exception-handling</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>try-except</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O11" t="b">
+        <v>0</v>
+      </c>
+      <c r="P11" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="b">
+        <v>1</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>a b c
+1</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>x
+5</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>1 2
+-1</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>p
+0</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>p</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>p q
+abc</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>red blue
+0</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>a b
+2</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>items=input().split()
+try: print(items[int(input())])
+except (ValueError,IndexError): print("Error")</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AH11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>explanation</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>score</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>difficulty</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>bloomTaxonomy</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>tags</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>subjects</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>topics</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>subTopics</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>companies</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>codingType</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>language</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>supportAllLanguages</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>enablePartialScore</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>ignoreCase</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>testcase1_input</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>testcase1_output</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>testcase2_input</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>testcase2_output</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>testcase3_input</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>testcase3_output</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>testcase4_input</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>testcase4_output</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>testcase5_input</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>testcase5_output</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>testcase6_input</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>testcase6_output</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>testcase7_input</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>testcase7_output</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>preloadCode_python</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>solution_python</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>hints</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
           <t>Python - Validate Registration</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t xml:space="preserve">
 Registrations for the inter-college hackathon are pouring in, and Anu must reject badly filled forms with a clear reason. Write a program that reads a name, an age, and an email, and checks them in order: the name must not be empty, the age must be a whole number from 1 to 120, and the email must contain '@'. Print 'Valid' if all three checks pass; otherwise print only the first failure: 'Invalid name', 'Invalid age', or 'Invalid email'.
@@ -1927,138 +2514,148 @@
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D2" t="n">
         <v>5</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
         <is>
           <t>exception-handling</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>validation</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>raising-exceptions</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O10" t="b">
+      <c r="O2" t="b">
         <v>0</v>
       </c>
-      <c r="P10" t="b">
+      <c r="P2" t="b">
         <v>1</v>
       </c>
-      <c r="Q10" t="b">
+      <c r="Q2" t="b">
         <v>1</v>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>Asha
 20
 asha@x.com</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>Valid</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Bob
 200
 b@x.com</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>Invalid age</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>Sam
 25
 samx.com</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>Invalid email</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t xml:space="preserve">
 20
 a@x.com</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>Invalid name</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>Meera
 abc
 m@x.com</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>Invalid age</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>Zed
 0
 z@x.com</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>Invalid age</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>Kabir
 120
 k@x.com</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>Valid</t>
         </is>
       </c>
-      <c r="AG10" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>name = input()
 age_text = input()
@@ -2080,13 +2677,13 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="3">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Python - Calculator with Errors</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t xml:space="preserve">
 Uncle Prakash's stationery shop runs a small calculator program at the billing counter, and it must never crash mid-billing no matter what gets typed. Write a program that reads a number, an operator (+, -, *, or /), and a second number, then prints the result of applying the operator. If the customer tries to divide by zero, print 'Cannot divide by zero'; if the operator is not one of the four, print 'Unknown operator'.
@@ -2105,138 +2702,148 @@
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D3" t="n">
         <v>5</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>exception-handling</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>try-except</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>exception-handling-patterns</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O11" t="b">
+      <c r="O3" t="b">
         <v>0</v>
       </c>
-      <c r="P11" t="b">
+      <c r="P3" t="b">
         <v>1</v>
       </c>
-      <c r="Q11" t="b">
+      <c r="Q3" t="b">
         <v>1</v>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>6
 /
 0</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>Cannot divide by zero</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>5
 %
 2</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Unknown operator</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>10
 +
 5</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>0
 *
 5</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>-6
 -
 2</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>7
 /
 2</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>10
 ^
 3</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>Unknown operator</t>
         </is>
       </c>
-      <c r="AG11" t="inlineStr">
+      <c r="AG3" t="inlineStr">
         <is>
           <t>a = int(input())
 op = input()
@@ -2259,13 +2866,13 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Python - Safe Integer</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Read a line and try to treat it as a whole number, printing double its value. If it is not a valid number, print 'Not a number'.
 ### Input Format
@@ -2274,130 +2881,142 @@
 ```
 10
 ```
+### Example Walkthrough
+In the sample, the input is `5`. It converts to an integer cleanly, and doubling it gives `10`, so the program prints `10`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D4" t="n">
         <v>5</v>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t>exception-handling</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>try-except</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O12" t="b">
+      <c r="O4" t="b">
         <v>0</v>
       </c>
-      <c r="P12" t="b">
+      <c r="P4" t="b">
         <v>1</v>
       </c>
-      <c r="Q12" t="b">
+      <c r="Q4" t="b">
         <v>1</v>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>abc</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Not a number</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>-6</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>3.5</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>Not a number</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
 </t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>Not a number</t>
         </is>
       </c>
-      <c r="AD12" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>999999</t>
         </is>
       </c>
-      <c r="AE12" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>1999998</t>
         </is>
       </c>
-      <c r="AG12" t="inlineStr">
+      <c r="AG4" t="inlineStr">
         <is>
           <t>text = input()
 try:
@@ -2407,13 +3026,13 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Python - Safe Float</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Read a line and try to treat it as a decimal number, printing it rounded to 2 decimal places. If it is not valid, print 'Invalid'.
 ### Input Format
@@ -2422,130 +3041,142 @@
 ```
 3.14
 ```
+### Example Walkthrough
+In the sample, the input is `3.14`. It converts to a float cleanly, and rounding to 2 decimal places leaves it as `3.14`, so the program prints `3.14`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D13" t="n">
+      <c r="D5" t="n">
         <v>5</v>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
         <is>
           <t>exception-handling</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>try-except</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O13" t="b">
+      <c r="O5" t="b">
         <v>0</v>
       </c>
-      <c r="P13" t="b">
+      <c r="P5" t="b">
         <v>1</v>
       </c>
-      <c r="Q13" t="b">
+      <c r="Q5" t="b">
         <v>1</v>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>3.14159</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>3.14</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>hello</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>Invalid</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>-1.005</t>
         </is>
       </c>
-      <c r="AA13" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>-1.0</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
 </t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>Invalid</t>
         </is>
       </c>
-      <c r="AD13" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>1e10</t>
         </is>
       </c>
-      <c r="AE13" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>10000000000.0</t>
         </is>
       </c>
-      <c r="AG13" t="inlineStr">
+      <c r="AG5" t="inlineStr">
         <is>
           <t>text = input()
 try:
@@ -2555,13 +3186,13 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Python - Add Two Safely</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Read two lines and print their sum as whole numbers. If either line is not a valid number, print 'Invalid input'.
 ### Input Format
@@ -2571,136 +3202,148 @@
 ```
 7
 ```
+### Example Walkthrough
+In the sample, the values are `3` and `4`. Both convert cleanly, and adding them gives `7`, so the program prints `7`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D14" t="n">
+      <c r="D6" t="n">
         <v>5</v>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
         <is>
           <t>exception-handling</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>try-except</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O14" t="b">
+      <c r="O6" t="b">
         <v>0</v>
       </c>
-      <c r="P14" t="b">
+      <c r="P6" t="b">
         <v>1</v>
       </c>
-      <c r="Q14" t="b">
+      <c r="Q6" t="b">
         <v>1</v>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>3
 4</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>x
 5</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>Invalid input</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>10
 20</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>0
 0</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>-5
 5</t>
         </is>
       </c>
-      <c r="AA14" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>7
 y</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>Invalid input</t>
         </is>
       </c>
-      <c r="AD14" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>100
 200</t>
         </is>
       </c>
-      <c r="AE14" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>300</t>
         </is>
       </c>
-      <c r="AG14" t="inlineStr">
+      <c r="AG6" t="inlineStr">
         <is>
           <t>try:
     a = int(input())
@@ -2711,13 +3354,13 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Python - Sum Valid Numbers</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Read a line of tokens separated by spaces and print the sum of only the ones that are valid whole numbers, ignoring the rest.
 ### Input Format
@@ -2726,129 +3369,141 @@
 ```
 6
 ```
+### Example Walkthrough
+In the sample, the tokens are `1 two 2 three 3`. Only `1`, `2`, and `3` are valid numbers, and they sum to `6`, so the program prints `6`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D15" t="n">
+      <c r="D7" t="n">
         <v>5</v>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
         <is>
           <t>exception-handling</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>try-except</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O15" t="b">
+      <c r="O7" t="b">
         <v>0</v>
       </c>
-      <c r="P15" t="b">
+      <c r="P7" t="b">
         <v>1</v>
       </c>
-      <c r="Q15" t="b">
+      <c r="Q7" t="b">
         <v>1</v>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>1 2 x 3</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>a b</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>10 20 hi 30</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>-1 -2 3</t>
         </is>
       </c>
-      <c r="AA15" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>1 2 3 4</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="AD15" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>x y z</t>
         </is>
       </c>
-      <c r="AE15" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AG15" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>total = 0
 for token in input().split():
@@ -2860,13 +3515,13 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Python - Safe Modulo</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Read two whole numbers and print the remainder of the first divided by the second. If the second is zero, print 'Cannot mod by zero'.
 ### Input Format
@@ -2876,136 +3531,148 @@
 ```
 1
 ```
+### Example Walkthrough
+In the sample, the numbers are `7` and `3`. Since `7 % 3 = 1`, the program prints `1`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D16" t="n">
+      <c r="D8" t="n">
         <v>5</v>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
         <is>
           <t>exception-handling</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>try-except</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O16" t="b">
+      <c r="O8" t="b">
         <v>0</v>
       </c>
-      <c r="P16" t="b">
+      <c r="P8" t="b">
         <v>1</v>
       </c>
-      <c r="Q16" t="b">
+      <c r="Q8" t="b">
         <v>1</v>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>10
 3</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>5
 0</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>Cannot mod by zero</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>8
 4</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>0
 5</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>-10
 3</t>
         </is>
       </c>
-      <c r="AA16" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>1
 1</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AD16" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>-8
 0</t>
         </is>
       </c>
-      <c r="AE16" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>Cannot mod by zero</t>
         </is>
       </c>
-      <c r="AG16" t="inlineStr">
+      <c r="AG8" t="inlineStr">
         <is>
           <t>a = int(input())
 b = int(input())
@@ -3016,13 +3683,13 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Python - Safe Square Root</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Read a number and print its square root. If the number is negative, the square root fails, so catch the error and print 'Cannot take square root of negative'.
 ### Input Format
@@ -3031,129 +3698,141 @@
 ```
 4.0
 ```
+### Example Walkthrough
+In the sample, the number is `16`. Its square root is `4.0`, so the program prints `4.0`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D17" t="n">
+      <c r="D9" t="n">
         <v>5</v>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
         <is>
           <t>exception-handling</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>try-except</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O17" t="b">
+      <c r="O9" t="b">
         <v>0</v>
       </c>
-      <c r="P17" t="b">
+      <c r="P9" t="b">
         <v>1</v>
       </c>
-      <c r="Q17" t="b">
+      <c r="Q9" t="b">
         <v>1</v>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>Cannot take square root of negative</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
+      <c r="Z9" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="AA17" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>Cannot take square root of negative</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AD17" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="AE17" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>10.0</t>
         </is>
       </c>
-      <c r="AG17" t="inlineStr">
+      <c r="AG9" t="inlineStr">
         <is>
           <t>import math
 n = int(input())
@@ -3164,13 +3843,536 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Python - Safe Key Lookup</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Safe Key Lookup. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: N
+- Next N lines: key value
+- Last line: key
+### Output Format
+```
+10
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>exception-handling</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>try-except</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O10" t="b">
+        <v>0</v>
+      </c>
+      <c r="P10" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="b">
+        <v>1</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>1
+a 10
+a</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>1
+a 10
+b</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Missing</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>0
+x</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Missing</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>2
+x 1
+y 2
+y</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>2
+x 1
+y 2
+z</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>Missing</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>1
+name Asha
+name</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Asha</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>1
+name Asha
+age</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>Missing</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>n=int(input()); d={}
+for _ in range(n):
+ k,v=input().split(); d[k]=v
+try: print(d[input()])
+except KeyError: print("Missing")</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Python - Finally Message</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Finally Message. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: Value
+### Output Format
+```
+5
+Done
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>exception-handling</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>exception-handling-patterns</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O11" t="b">
+        <v>0</v>
+      </c>
+      <c r="P11" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="b">
+        <v>1</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>5
+Done</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Invalid
+Done</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>0
+Done</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>-1
+Done</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Invalid
+Done</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>100
+Done</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>abc</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>Invalid
+Done</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>try: print(int(input()))
+except ValueError: print("Invalid")
+finally: print("Done")</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AH11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>explanation</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>score</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>difficulty</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>bloomTaxonomy</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>tags</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>subjects</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>topics</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>subTopics</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>companies</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>codingType</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>language</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>supportAllLanguages</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>enablePartialScore</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>ignoreCase</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>testcase1_input</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>testcase1_output</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>testcase2_input</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>testcase2_output</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>testcase3_input</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>testcase3_output</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>testcase4_input</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>testcase4_output</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>testcase5_input</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>testcase5_output</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>testcase6_input</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>testcase6_output</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>testcase7_input</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>testcase7_output</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>preloadCode_python</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>solution_python</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>hints</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Python - Else and Finally</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Read two numbers and divide them. Use an else block to print the result when it works, an except block to print 'Error' on divide-by-zero, and a finally block that always prints 'Checked'.
 ### Input Format
@@ -3181,143 +4383,155 @@
 4.0
 Checked
 ```
+### Example Walkthrough
+In the sample, the numbers are `8` and `2`. Dividing them gives `4.0`, printed by the else block, and the finally block always runs afterward, printing `Checked`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D18" t="n">
+      <c r="D2" t="n">
         <v>5</v>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
         <is>
           <t>exception-handling</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>try-except</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O18" t="b">
+      <c r="O2" t="b">
         <v>0</v>
       </c>
-      <c r="P18" t="b">
+      <c r="P2" t="b">
         <v>1</v>
       </c>
-      <c r="Q18" t="b">
+      <c r="Q2" t="b">
         <v>1</v>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>8
 2</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>4.0
 Checked</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>9
 0</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>Error
 Checked</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>10
 5</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>2.0
 Checked</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>0
 5</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>0.0
 Checked</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>-8
 2</t>
         </is>
       </c>
-      <c r="AA18" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>-4.0
 Checked</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>1
 1</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>1.0
 Checked</t>
         </is>
       </c>
-      <c r="AD18" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>-9
 0</t>
         </is>
       </c>
-      <c r="AE18" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>Error
 Checked</t>
         </is>
       </c>
-      <c r="AG18" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>a = int(input())
 b = int(input())
@@ -3332,13 +4546,13 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="3">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Python - Custom Exception</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Define a custom exception called NegativeError. Read a number and raise NegativeError if it is negative; catch it and print 'Negative not allowed'. Otherwise print the number's square.
 ### Input Format
@@ -3347,129 +4561,141 @@
 ```
 25
 ```
+### Example Walkthrough
+In the sample, the number is `5`, which is not negative, so `NegativeError` is never raised, and the program prints its square, `25`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D19" t="n">
+      <c r="D3" t="n">
         <v>5</v>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>exception-handling</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>raise-custom</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>custom-exceptions</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O19" t="b">
+      <c r="O3" t="b">
         <v>0</v>
       </c>
-      <c r="P19" t="b">
+      <c r="P3" t="b">
         <v>1</v>
       </c>
-      <c r="Q19" t="b">
+      <c r="Q3" t="b">
         <v>1</v>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Negative not allowed</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="AA19" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>Negative not allowed</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="AD19" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>-100</t>
         </is>
       </c>
-      <c r="AE19" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>Negative not allowed</t>
         </is>
       </c>
-      <c r="AG19" t="inlineStr">
+      <c r="AG3" t="inlineStr">
         <is>
           <t>class NegativeError(Exception):
     pass
@@ -3483,13 +4709,13 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Python - First Valid Number</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Read N lines and print the first one that is a valid whole number. If none of them are, print 'No valid number'.
 ### Input Format
@@ -3499,59 +4725,71 @@
 ```
 12
 ```
+### Example Walkthrough
+In the sample, `N` is `3` with the lines `abc`, `12`, and `34`. The first line that converts successfully is `12`, so the program prints `12`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D20" t="n">
+      <c r="D4" t="n">
         <v>5</v>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t>exception-handling</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>try-except</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>exception-handling-patterns</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O20" t="b">
+      <c r="O4" t="b">
         <v>0</v>
       </c>
-      <c r="P20" t="b">
+      <c r="P4" t="b">
         <v>1</v>
       </c>
-      <c r="Q20" t="b">
+      <c r="Q4" t="b">
         <v>1</v>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>3
 abc
@@ -3559,57 +4797,57 @@
 xyz</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>2
 x
 y</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>No valid number</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>2
 5
 6</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y20" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>No valid number</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>1
 abc</t>
         </is>
       </c>
-      <c r="AA20" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>No valid number</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>3
 x
@@ -3617,12 +4855,12 @@
 0</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AD20" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>4
 a
@@ -3631,12 +4869,12 @@
 -5</t>
         </is>
       </c>
-      <c r="AE20" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>-5</t>
         </is>
       </c>
-      <c r="AG20" t="inlineStr">
+      <c r="AG4" t="inlineStr">
         <is>
           <t>n = int(input())
 answer = "No valid number"
@@ -3651,13 +4889,13 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Python - Safe Nested Lookup</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Read a line of JSON and print the value at data['user']['name']. If any part of that path is missing, print 'Not available'.
 ### Input Format
@@ -3666,124 +4904,136 @@
 ```
 Asha
 ```
+### Example Walkthrough
+In the sample, the JSON is `{"user": {"name": "Asha"}}`. Both keys exist, so the program prints `Asha`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D21" t="n">
+      <c r="D5" t="n">
         <v>5</v>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
         <is>
           <t>exception-handling</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>try-except</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O21" t="b">
+      <c r="O5" t="b">
         <v>0</v>
       </c>
-      <c r="P21" t="b">
+      <c r="P5" t="b">
         <v>1</v>
       </c>
-      <c r="Q21" t="b">
+      <c r="Q5" t="b">
         <v>1</v>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>{"user": {"name": "Asha"}}</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>Asha</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>{"user": {}}</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>Not available</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>Not available</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>{"user": {"name": ""}}</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>{"other": 1}</t>
         </is>
       </c>
-      <c r="AA21" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>Not available</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>{"user": {"name": "Kabir", "age": 20}}</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>Kabir</t>
         </is>
       </c>
-      <c r="AD21" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>{"x": 1, "y": 2}</t>
         </is>
       </c>
-      <c r="AE21" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>Not available</t>
         </is>
       </c>
-      <c r="AG21" t="inlineStr">
+      <c r="AG5" t="inlineStr">
         <is>
           <t>import json
 data = json.loads(input())
@@ -3794,13 +5044,13 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Python - Index or Bad Input</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Read a line of numbers and an index. Print the value at that index, 'Invalid index' if the index is not a number, or 'Out of range' if it is too large.
 ### Input Format
@@ -3810,136 +5060,148 @@
 ```
 20
 ```
+### Example Walkthrough
+In the sample, the numbers are `10 20 30` and the index is `1`. Position `1` holds `20`, so the program prints `20`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D22" t="n">
+      <c r="D6" t="n">
         <v>5</v>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
         <is>
           <t>exception-handling</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>try-except</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>exception-handling-patterns</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O22" t="b">
+      <c r="O6" t="b">
         <v>0</v>
       </c>
-      <c r="P22" t="b">
+      <c r="P6" t="b">
         <v>1</v>
       </c>
-      <c r="Q22" t="b">
+      <c r="Q6" t="b">
         <v>1</v>
       </c>
-      <c r="R22" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>10 20 30
 1</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>1 2 3
 x</t>
         </is>
       </c>
-      <c r="U22" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>Invalid index</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>1 2 3
 9</t>
         </is>
       </c>
-      <c r="W22" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>Out of range</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>1 2 3
 0</t>
         </is>
       </c>
-      <c r="Y22" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>1 2 3
 -1</t>
         </is>
       </c>
-      <c r="AA22" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>5
 y</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>Invalid index</t>
         </is>
       </c>
-      <c r="AD22" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>1 2 3 4
 3</t>
         </is>
       </c>
-      <c r="AE22" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AG22" t="inlineStr">
+      <c r="AG6" t="inlineStr">
         <is>
           <t>nums = input().split()
 raw = input()
@@ -3953,13 +5215,13 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Python - Divide the List</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Read a line of numbers and a divisor. Print each number divided by the divisor (integer division), separated by spaces. If the divisor is zero, print 'Cannot divide' instead.
 ### Input Format
@@ -3969,136 +5231,148 @@
 ```
 5 10 15
 ```
+### Example Walkthrough
+In the sample, the numbers are `10 20 30` and the divisor is `2`. Dividing each gives `5`, `10`, and `15`, so the program prints `5 10 15`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D23" t="n">
+      <c r="D7" t="n">
         <v>5</v>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
         <is>
           <t>exception-handling</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>try-except</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O23" t="b">
+      <c r="O7" t="b">
         <v>0</v>
       </c>
-      <c r="P23" t="b">
+      <c r="P7" t="b">
         <v>1</v>
       </c>
-      <c r="Q23" t="b">
+      <c r="Q7" t="b">
         <v>1</v>
       </c>
-      <c r="R23" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>10 20 30
 2</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>5 10 15</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>5 6
 0</t>
         </is>
       </c>
-      <c r="U23" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>Cannot divide</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>9
 3</t>
         </is>
       </c>
-      <c r="W23" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>0
 5</t>
         </is>
       </c>
-      <c r="Y23" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>-10 -20
 2</t>
         </is>
       </c>
-      <c r="AA23" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>-5 -10</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>1
 1</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AD23" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>-9
 0</t>
         </is>
       </c>
-      <c r="AE23" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>Cannot divide</t>
         </is>
       </c>
-      <c r="AG23" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>nums = list(map(int, input().split()))
 divisor = int(input())
@@ -4110,13 +5384,13 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Python - Safe Average</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Read N, then N numbers on separate lines, and print their average. If N is zero there is no data, so catch the division error and print 'No data'.
 ### Input Format
@@ -4126,59 +5400,71 @@
 ```
 20.0
 ```
+### Example Walkthrough
+In the sample, `N` is `3` with values `10`, `20`, and `30`. Their average is `20.0`, so the program prints `20.0`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D24" t="n">
+      <c r="D8" t="n">
         <v>5</v>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
         <is>
           <t>exception-handling</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>try-except</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O24" t="b">
+      <c r="O8" t="b">
         <v>0</v>
       </c>
-      <c r="P24" t="b">
+      <c r="P8" t="b">
         <v>1</v>
       </c>
-      <c r="Q24" t="b">
+      <c r="Q8" t="b">
         <v>1</v>
       </c>
-      <c r="R24" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>3
 10
@@ -4186,56 +5472,56 @@
 30</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>20.0</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U24" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>No data</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>1
 50</t>
         </is>
       </c>
-      <c r="W24" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>50.0</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>2
 -5
 5</t>
         </is>
       </c>
-      <c r="Y24" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>1
 0</t>
         </is>
       </c>
-      <c r="AA24" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>4
 1
@@ -4244,24 +5530,24 @@
 4</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>2.5</t>
         </is>
       </c>
-      <c r="AD24" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>2
 100
 200</t>
         </is>
       </c>
-      <c r="AE24" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>150.0</t>
         </is>
       </c>
-      <c r="AG24" t="inlineStr">
+      <c r="AG8" t="inlineStr">
         <is>
           <t>n = int(input())
 nums = [int(input()) for _ in range(n)]
@@ -4272,13 +5558,697 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Python - Raise Age Error</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Raise Age Error. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: Age
+### Output Format
+```
+Valid
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>exception-handling</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>raising-exceptions</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O9" t="b">
+        <v>0</v>
+      </c>
+      <c r="P9" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="b">
+        <v>1</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>Valid</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Invalid age</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Valid</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Valid</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>Valid</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>-99</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Invalid age</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>Valid</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>try:
+ age=int(input())
+ if age&lt;0: raise ValueError()
+ print("Valid")
+except ValueError: print("Invalid age")</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Python - Retry First Valid</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Retry First Valid. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: N
+- Next N lines: Values
+### Output Format
+```
+5
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>exception-handling</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>defensive-programming</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O10" t="b">
+        <v>0</v>
+      </c>
+      <c r="P10" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="b">
+        <v>1</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>3
+a
+5
+6</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>2
+x
+y</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>1
+10</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>4
+no
+3.5
+-2
+9</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>3
+1
+2
+3</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>2
+blank
+7</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>n=int(input()); found=False
+for _ in range(n):
+ v=input()
+ if not found:
+  try: print(int(v)); found=True
+  except ValueError: pass
+if not found: print("None")</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Python - Custom Low Balance</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Custom Low Balance. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: Balance
+- Line 2: Withdrawal
+### Output Format
+```
+Balance 70.0
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>exception-handling</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>custom-exceptions</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O11" t="b">
+        <v>0</v>
+      </c>
+      <c r="P11" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="b">
+        <v>1</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>100
+30</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>Balance 70.0</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>50
+60</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Insufficient</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>0
+0</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Balance 0.0</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>10
+10</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Balance 0.0</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>-5
+1</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Insufficient</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>100.5
+0.5</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Balance 100.0</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>5
+4</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>Balance 1.0</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>class LowBalanceError(Exception): pass
+try:
+ b=float(input()); w=float(input())
+ if w&gt;b: raise LowBalanceError()
+ print("Balance", b-w)
+except LowBalanceError: print("Insufficient")</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AH11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>explanation</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>score</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>difficulty</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>bloomTaxonomy</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>tags</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>subjects</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>topics</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>subTopics</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>companies</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>codingType</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>language</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>supportAllLanguages</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>enablePartialScore</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>ignoreCase</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>testcase1_input</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>testcase1_output</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>testcase2_input</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>testcase2_output</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>testcase3_input</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>testcase3_output</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>testcase4_input</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>testcase4_output</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>testcase5_input</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>testcase5_output</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>testcase6_input</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>testcase6_output</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>testcase7_input</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>testcase7_output</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>preloadCode_python</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>solution_python</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>hints</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Python - Parse CSV Safely</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Read N lines, each meant to be 'name,age'. A line is valid only if it has exactly two fields, a non-empty name, and an age that is a whole number. Print the names from the valid lines, one per line.
 ### Input Format
@@ -4288,59 +6258,71 @@
 ```
 asha
 ```
+### Example Walkthrough
+In the sample, `N` is `2` with records `asha,20` and `kabir,x`. The first record is valid and prints `asha`; the second has a non-numeric age and is skipped.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D25" t="n">
+      <c r="D2" t="n">
         <v>5</v>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
         <is>
           <t>exception-handling</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>validation</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>defensive-programming</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O25" t="b">
+      <c r="O2" t="b">
         <v>0</v>
       </c>
-      <c r="P25" t="b">
+      <c r="P2" t="b">
         <v>1</v>
       </c>
-      <c r="Q25" t="b">
+      <c r="Q2" t="b">
         <v>1</v>
       </c>
-      <c r="R25" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>3
 asha,20
@@ -4348,53 +6330,53 @@
 sam,x</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>asha</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>2
 a,10
 b,20</t>
         </is>
       </c>
-      <c r="U25" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>a
 b</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>2
 x,5
 ,7</t>
         </is>
       </c>
-      <c r="W25" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>1
 zed,1</t>
         </is>
       </c>
-      <c r="AA25" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>zed</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>4
 a,1,2
@@ -4403,18 +6385,18 @@
 d,x</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>b</t>
         </is>
       </c>
-      <c r="AD25" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>1
 ,10</t>
         </is>
       </c>
-      <c r="AG25" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>n = int(input())
 for _ in range(n):
@@ -4433,13 +6415,13 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+    <row r="3">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Python - Password Strength</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Read a password. It must be at least 6 characters long and contain at least one digit. Print 'Strong' if both hold, 'Too short' if it is under 6 characters, or 'Needs a digit' if it has no digit.
 ### Input Format
@@ -4448,130 +6430,142 @@
 ```
 Strong
 ```
+### Example Walkthrough
+In the sample, the password is `abcdef1`. It has `7` characters (at least `6`) and contains a digit, so the program prints `Strong`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D26" t="n">
+      <c r="D3" t="n">
         <v>5</v>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>exception-handling</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>raise-custom</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>custom-exceptions</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O26" t="b">
+      <c r="O3" t="b">
         <v>0</v>
       </c>
-      <c r="P26" t="b">
+      <c r="P3" t="b">
         <v>1</v>
       </c>
-      <c r="Q26" t="b">
+      <c r="Q3" t="b">
         <v>1</v>
       </c>
-      <c r="R26" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>abc123</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>Strong</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>ab1</t>
         </is>
       </c>
-      <c r="U26" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Too short</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>abcdef</t>
         </is>
       </c>
-      <c r="W26" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>Needs a digit</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>123456</t>
         </is>
       </c>
-      <c r="Y26" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>Strong</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>abcde1</t>
         </is>
       </c>
-      <c r="AA26" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>Strong</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
 </t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>Too short</t>
         </is>
       </c>
-      <c r="AD26" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>abc12345</t>
         </is>
       </c>
-      <c r="AE26" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>Strong</t>
         </is>
       </c>
-      <c r="AG26" t="inlineStr">
+      <c r="AG3" t="inlineStr">
         <is>
           <t>class WeakPassword(Exception):
     pass
@@ -4587,13 +6581,13 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Python - Safe JSON Parse</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Read one line and try to parse it as a JSON object. If it is not valid JSON, print 'Invalid JSON'. Otherwise print how many keys the object has.
 ### Input Format
@@ -4602,129 +6596,141 @@
 ```
 2
 ```
+### Example Walkthrough
+In the sample, the JSON is `{"a": 1, "b": 2}`. It parses successfully and has `2` keys, so the program prints `2`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D27" t="n">
+      <c r="D4" t="n">
         <v>5</v>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t>exception-handling</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>try-except</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O27" t="b">
+      <c r="O4" t="b">
         <v>0</v>
       </c>
-      <c r="P27" t="b">
+      <c r="P4" t="b">
         <v>1</v>
       </c>
-      <c r="Q27" t="b">
+      <c r="Q4" t="b">
         <v>1</v>
       </c>
-      <c r="R27" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>{"a": 1, "b": 2}</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>not json</t>
         </is>
       </c>
-      <c r="U27" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Invalid JSON</t>
         </is>
       </c>
-      <c r="V27" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
-      <c r="W27" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>{"single": 1}</t>
         </is>
       </c>
-      <c r="Y27" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>[1,2,3]</t>
         </is>
       </c>
-      <c r="AA27" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>{invalid</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>Invalid JSON</t>
         </is>
       </c>
-      <c r="AD27" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>{"a":1,"b":2,"c":3}</t>
         </is>
       </c>
-      <c r="AE27" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AG27" t="inlineStr">
+      <c r="AG4" t="inlineStr">
         <is>
           <t>import json
 line = input()
@@ -4736,13 +6742,13 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Python - Grade with Validation</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Read a mark. If it is not between 0 and 100, print 'Invalid marks'. Otherwise print the grade: 'A' for 90 or more, 'B' for 75 or more, 'C' for 60 or more, and 'F' below that.
 ### Input Format
@@ -4751,129 +6757,141 @@
 ```
 A
 ```
+### Example Walkthrough
+In the sample, the mark is `95`. Since `95` is at least `90`, the program prints `A`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D28" t="n">
+      <c r="D5" t="n">
         <v>5</v>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
         <is>
           <t>exception-handling</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>validation</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>raising-exceptions</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O28" t="b">
+      <c r="O5" t="b">
         <v>0</v>
       </c>
-      <c r="P28" t="b">
+      <c r="P5" t="b">
         <v>1</v>
       </c>
-      <c r="Q28" t="b">
+      <c r="Q5" t="b">
         <v>1</v>
       </c>
-      <c r="R28" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>95</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>150</t>
         </is>
       </c>
-      <c r="U28" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>Invalid marks</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="W28" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y28" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="AA28" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>-5</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>Invalid marks</t>
         </is>
       </c>
-      <c r="AD28" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>59</t>
         </is>
       </c>
-      <c r="AE28" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="AG28" t="inlineStr">
+      <c r="AG5" t="inlineStr">
         <is>
           <t>marks = int(input())
 try:
@@ -4892,13 +6910,13 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Python - Batch Convert</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Read N values on separate lines and try to convert each to a whole number. Print 'ok X fail Y' with the counts of successful and failed conversions.
 ### Input Format
@@ -4908,59 +6926,71 @@
 ```
 ok 3 fail 1
 ```
+### Example Walkthrough
+In the sample, `N` is `4` with values `1`, `2`, `x`, and `3`. Three convert successfully and one fails, so the program prints `ok 3 fail 1`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D29" t="n">
+      <c r="D6" t="n">
         <v>5</v>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
         <is>
           <t>exception-handling</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>try-except</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>exception-handling-patterns</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O29" t="b">
+      <c r="O6" t="b">
         <v>0</v>
       </c>
-      <c r="P29" t="b">
+      <c r="P6" t="b">
         <v>1</v>
       </c>
-      <c r="Q29" t="b">
+      <c r="Q6" t="b">
         <v>1</v>
       </c>
-      <c r="R29" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>4
 1
@@ -4969,56 +6999,56 @@
 3</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>ok 3 fail 1</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>2
 a
 b</t>
         </is>
       </c>
-      <c r="U29" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>ok 0 fail 2</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>1
 5</t>
         </is>
       </c>
-      <c r="W29" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>ok 1 fail 0</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y29" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>ok 0 fail 0</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>1
 0</t>
         </is>
       </c>
-      <c r="AA29" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>ok 1 fail 0</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>3
 -1
@@ -5026,12 +7056,12 @@
 -3</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>ok 3 fail 0</t>
         </is>
       </c>
-      <c r="AD29" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>5
 1
@@ -5041,12 +7071,12 @@
 5</t>
         </is>
       </c>
-      <c r="AE29" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>ok 5 fail 0</t>
         </is>
       </c>
-      <c r="AG29" t="inlineStr">
+      <c r="AG6" t="inlineStr">
         <is>
           <t>n = int(input())
 ok = fail = 0
@@ -5060,13 +7090,13 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Python - Safe Matrix Access</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Read a grid with R rows and C columns, then Q queries, each a row and column. For each query print the value at that position, or 'Out of bounds' if the position is outside the grid.
 ### Input Format
@@ -5079,59 +7109,71 @@
 2
 Out of bounds
 ```
+### Example Walkthrough
+In the sample, the grid is `2` by `2`: `1 2` and `3 4`, with `2` queries. The first query `0 1` reads the grid position and prints `2`; the second query `5 5` falls outside the grid, so the program prints `Out of bounds`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D30" t="n">
+      <c r="D7" t="n">
         <v>5</v>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
         <is>
           <t>exception-handling</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>try-except</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>exception-handling-patterns</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O30" t="b">
+      <c r="O7" t="b">
         <v>0</v>
       </c>
-      <c r="P30" t="b">
+      <c r="P7" t="b">
         <v>1</v>
       </c>
-      <c r="Q30" t="b">
+      <c r="Q7" t="b">
         <v>1</v>
       </c>
-      <c r="R30" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>2 2
 1 2
@@ -5141,13 +7183,13 @@
 5 5</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>2
 Out of bounds</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>1 1
 9
@@ -5155,12 +7197,12 @@
 0 0</t>
         </is>
       </c>
-      <c r="U30" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="V30" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>2 2
 1 2
@@ -5169,12 +7211,12 @@
 1 1</t>
         </is>
       </c>
-      <c r="W30" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>1 1
 5
@@ -5182,19 +7224,19 @@
 -1 0</t>
         </is>
       </c>
-      <c r="Y30" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>Out of bounds</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>1 1
 5
 0</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>3 3
 1 2 3
@@ -5205,13 +7247,13 @@
 0 0</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>9
 1</t>
         </is>
       </c>
-      <c r="AD30" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>2 2
 1 2
@@ -5220,12 +7262,12 @@
 10 10</t>
         </is>
       </c>
-      <c r="AE30" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>Out of bounds</t>
         </is>
       </c>
-      <c r="AG30" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>r, c = map(int, input().split())
 grid = [list(map(int, input().split())) for _ in range(r)]
@@ -5241,13 +7283,13 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Python - Robust Statistics</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Read a line of tokens. Compute the average of the ones that are valid numbers, printed to 1 decimal place. If none of the tokens are valid numbers, print 'No valid data'.
 ### Input Format
@@ -5256,129 +7298,141 @@
 ```
 20.0
 ```
+### Example Walkthrough
+In the sample, the tokens are `10 x 20 y 30`. Only `10`, `20`, and `30` are valid numbers, and their average is `20.0`, so the program prints `20.0`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D31" t="n">
+      <c r="D8" t="n">
         <v>5</v>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
         <is>
           <t>exception-handling</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>try-except</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>defensive-programming</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O31" t="b">
+      <c r="O8" t="b">
         <v>0</v>
       </c>
-      <c r="P31" t="b">
+      <c r="P8" t="b">
         <v>1</v>
       </c>
-      <c r="Q31" t="b">
+      <c r="Q8" t="b">
         <v>1</v>
       </c>
-      <c r="R31" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>10 20 x 30</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>20.0</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>a b c</t>
         </is>
       </c>
-      <c r="U31" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>No valid data</t>
         </is>
       </c>
-      <c r="V31" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>5 5</t>
         </is>
       </c>
-      <c r="W31" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>0 0</t>
         </is>
       </c>
-      <c r="Y31" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>-5 5 -10</t>
         </is>
       </c>
-      <c r="AA31" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>-3.3</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>1 2 3 4 5</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AD31" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>x y 10</t>
         </is>
       </c>
-      <c r="AE31" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>10.0</t>
         </is>
       </c>
-      <c r="AG31" t="inlineStr">
+      <c r="AG8" t="inlineStr">
         <is>
           <t>numbers = []
 for token in input().split():
@@ -5393,6 +7447,504 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Python - Parse Marks Safely</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Parse Marks Safely. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: Values
+### Output Format
+```
+15.0
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>exception-handling</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>defensive-programming</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O9" t="b">
+        <v>0</v>
+      </c>
+      <c r="P9" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="b">
+        <v>1</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>10 20 x</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>15.0</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>a b</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>No valid marks</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>-5 5</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>1 2 3</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>0 x 0</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>3.5 4</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>marks=[]
+for v in input().split():
+ try: marks.append(int(v))
+ except ValueError: pass
+print(sum(marks)/len(marks) if marks else "No valid marks")</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Python - Nested Safe Access</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Nested Safe Access. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: Rows
+- Next rows: values
+- Line: row index
+- Line: col index
+### Output Format
+```
+2
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>exception-handling</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>exception-handling-patterns</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O10" t="b">
+        <v>0</v>
+      </c>
+      <c r="P10" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="b">
+        <v>1</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>2
+1 2
+3 4
+0
+1</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>1
+5
+2
+0</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>2
+1
+2
+0
+5</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>0
+0
+0</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>2
+1 2
+3 4
+a
+0</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>2
+1 2
+3 4
+1
+0</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>1
+9
+0
+0</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>rows=int(input()); m=[]
+for _ in range(rows): m.append(input().split())
+try: print(m[int(input())][int(input())])
+except (ValueError,IndexError): print("Error")</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Python - Validate Password</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Validate Password. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: Password
+### Output Format
+```
+Strong
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>exception-handling</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>raising-exceptions</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O11" t="b">
+        <v>0</v>
+      </c>
+      <c r="P11" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="b">
+        <v>1</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>abc123</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>abcdef</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>a1</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>password1</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>123456</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>ABCDEF1</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>try:
+ p=input()
+ if len(p)&lt;6: raise ValueError()
+ if not any(ch.isdigit() for ch in p): raise ValueError()
+ print("Strong")
+except ValueError: print("Weak")</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/content/Question Bank/Coding Questions/Unit 12 - Exception Handling/Unit 12 - Exception Handling - Coding Questions.xlsx
+++ b/content/Question Bank/Coding Questions/Unit 12 - Exception Handling/Unit 12 - Exception Handling - Coding Questions.xlsx
@@ -1993,16 +1993,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Safe Integer Input. Read the input values and print the required result exactly.
+          <t>A quiz app reads a player's numeric answer from a text box, but sometimes players type letters by mistake instead of a number; the app must catch that mistake instead of crashing.
+Write a program that reads a line of input inside a `try` block, converts it to an integer, and prints it. If the conversion raises a `ValueError` (the text isn't a valid whole number), catch it and print `Invalid` instead.
 ### Input Format
-- Line 1: Value
+- Line 1: A value that may or may not be a whole number
 ### Output Format
 ```
 10
 ```
+### Example Walkthrough
+In the sample, the input is `10`, which converts to an integer without error, so the program prints `10`. An input like `abc` would raise a `ValueError` and print `Invalid` instead.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- The input is a single line of text.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -2148,17 +2151,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Safe List Index. Read the input values and print the required result exactly.
+          <t>A playlist app lets a user jump to a song by its position number, but the number they type might be out of range or not a number at all, so the app needs to catch both kinds of mistakes gracefully instead of crashing.
+Write a program that reads a line of space-separated items into a list, then reads a position, and prints the item at that position (a negative position is valid and counts from the end, as in normal Python indexing). If the position is not a valid whole number, or is out of range, catch the error and print `Error`.
 ### Input Format
-- Line 1: Items
-- Line 2: Index
+- Line 1: Space-separated items
+- Line 2: A position
 ### Output Format
 ```
 b
 ```
+### Example Walkthrough
+In the sample, the items are `a b c` and the position is `1`. The item at position 1 is `b`, so the program prints `b`. A position of `5` (out of range) would print `Error` instead.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- The items line is a valid, non-empty line of space-separated values.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -3851,18 +3857,21 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Safe Key Lookup. Read the input values and print the required result exactly.
+          <t>A student ID lookup kiosk stores registered names mapped to their ID numbers; if someone types a name that was never registered, the kiosk should report it as missing instead of crashing.
+Write a program that reads a whole number N, then reads N lines each with a name and an ID separated by a space and stores them in a dictionary, then reads one more name and prints its ID. If the name is not in the dictionary, catch the `KeyError` and print `Missing` instead.
 ### Input Format
-- Line 1: N
-- Next N lines: key value
-- Last line: key
+- Line 1: N, the number of registered names
+- Next N lines: name and ID separated by a space
+- Final line: the name being looked up
 ### Output Format
 ```
 10
 ```
+### Example Walkthrough
+In the sample, N is 1 with `a 10` registered, and the query is `a`. Since `a` is in the dictionary with ID `10`, the program prints `10`. A query for an unregistered name would print `Missing` instead.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- Names and IDs are valid strings with no spaces within them.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -4025,17 +4034,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Finally Message. Read the input values and print the required result exactly.
+          <t>A device-connection routine always needs to print a closing status message, whether the connection attempt succeeded or failed, so the cleanup step is written inside a `finally` block that runs no matter what happens.
+Write a program that reads a line inside a `try` block, converts it to an integer, and prints it; if conversion raises a `ValueError`, catch it and print `Invalid` instead. Either way, use a `finally` block to print `Done` as the last line.
 ### Input Format
-- Line 1: Value
+- Line 1: A value that may or may not be a whole number
 ### Output Format
 ```
 5
 Done
 ```
+### Example Walkthrough
+In the sample, the input is `5`, which converts successfully and prints `5`, and then the `finally` block always runs and prints `Done`. An input like `x` would print `Invalid` followed by `Done`.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- The input is a single line of text.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -5566,16 +5578,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Raise Age Error. Read the input values and print the required result exactly.
+          <t>A hospital registration form accepts a patient's age, but a negative age makes no sense, so the form manually raises an error when it sees one and reports the entry as invalid.
+Write a program that reads a whole number age inside a `try` block; if the age is negative, manually `raise ValueError()`. Catch that error and print `Invalid age`; otherwise print `Valid`.
 ### Input Format
 - Line 1: Age
 ### Output Format
 ```
 Valid
 ```
+### Example Walkthrough
+In the sample, the age is 18, which is not negative, so no error is raised and the program prints `Valid`. An age of `-1` would raise the error and print `Invalid age` instead.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- All numeric inputs are valid whole numbers in the ranges implied by the examples.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -5723,17 +5738,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Retry First Valid. Read the input values and print the required result exactly.
+          <t>A sensor-reading pipeline gets a batch of raw readings that sometimes include garbled, non-numeric entries; the software needs to skip over the bad readings and report the very first valid numeric reading it finds.
+Write a program that reads a whole number N, then reads N more lines one at a time, trying to convert each to an integer inside a `try` block; skip (using `except ValueError: pass`) any line that fails to convert, and print the first one that succeeds. If none of the N lines are valid numbers, print `None`.
 ### Input Format
-- Line 1: N
-- Next N lines: Values
+- Line 1: N, the number of readings
+- Next N lines: raw readings, which may or may not be valid whole numbers
 ### Output Format
 ```
 5
 ```
+### Example Walkthrough
+In the sample, N is 3 with readings `a`, `5`, and `6`. The first reading `a` fails to convert and is skipped, the second reading `5` converts successfully, so the program prints `5` and stops checking further readings.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- N is a valid whole number matching the number of lines that follow.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -5898,17 +5916,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Custom Low Balance. Read the input values and print the required result exactly.
+          <t>A banking app defines its own custom exception, `LowBalanceError`, to clearly signal when a withdrawal would exceed the account balance, rather than reusing a generic built-in exception for something this specific.
+Define a class `LowBalanceError` that inherits from `Exception`. Write a program that reads a balance and a withdrawal amount; if the withdrawal is greater than the balance, `raise LowBalanceError()`. Catch that error and print `Insufficient`; otherwise print `Balance` followed by the balance after the withdrawal.
 ### Input Format
 - Line 1: Balance
-- Line 2: Withdrawal
+- Line 2: Withdrawal amount
 ### Output Format
 ```
 Balance 70.0
 ```
+### Example Walkthrough
+In the sample, the balance is 100 and the withdrawal is 30. Since 30 does not exceed 100, no error is raised, and the remaining balance is 100 - 30 = 70.0, so the program prints `Balance 70.0`.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- All numeric inputs are valid numbers in the ranges implied by the examples.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -7455,16 +7476,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Parse Marks Safely. Read the input values and print the required result exactly.
+          <t>A results-upload tool receives a row of marks typed by a teacher, but sometimes a cell contains a stray letter instead of a number; the tool should skip just the bad entries and still compute the average of the valid marks.
+Write a program that reads a line of space-separated values, tries to convert each one to an integer inside a `try` block (skipping any that raise `ValueError`), and prints the average of the values that converted successfully. If none of them are valid numbers, print `No valid marks`.
 ### Input Format
-- Line 1: Values
+- Line 1: Space-separated values, which may or may not all be valid whole numbers
 ### Output Format
 ```
 15.0
 ```
+### Example Walkthrough
+In the sample, the values are `10 20 x`. `10` and `20` convert successfully but `x` does not and is skipped, so the average of the valid marks is (10 + 20) / 2 = 15.0, which the program prints.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- The input line has at least one value.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -7612,19 +7636,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Nested Safe Access. Read the input values and print the required result exactly.
+          <t>A seating-chart app looks up whether a specific seat, given as a row and column number, is occupied in a grid stored as a list of lists, and must handle both coordinates that are out of range and inputs that aren't numbers at all.
+Write a program that reads a whole number `rows`, then reads `rows` lines each with space-separated values to build a grid (a list of lists), then reads a row index and a column index, and prints the value at that position. If either index is not a valid whole number, or is out of range, catch the error and print `Error`.
 ### Input Format
-- Line 1: Rows
-- Next rows: values
-- Line: row index
-- Line: col index
+- Line 1: Number of rows
+- Next `rows` lines: space-separated values for that row
+- Next line: row index to look up
+- Final line: column index to look up
 ### Output Format
 ```
 2
 ```
+### Example Walkthrough
+In the sample, the grid has 2 rows, `1 2` and `3 4`, and the lookup is row `0`, column `1`. The value at row 0, column 1 is `2`, so the program prints `2`.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- All numeric inputs are valid whole numbers in the ranges implied by the examples.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -7795,16 +7822,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Validate Password. Read the input values and print the required result exactly.
+          <t>A signup form checks whether a new password is strong enough (at least 6 characters long and containing at least one digit), manually raising an error internally for either failing condition and catching it to report the password as weak.
+Write a program that reads a password inside a `try` block; if it is shorter than 6 characters, or contains no digits, `raise ValueError()`. Catch that error and print `Weak`; otherwise print `Strong`.
 ### Input Format
-- Line 1: Password
+- Line 1: A password
 ### Output Format
 ```
 Strong
 ```
+### Example Walkthrough
+In the sample, the password is `abc123`. It has 6 characters and contains digits, so neither condition raises an error, and the program prints `Strong`. A password like `abcdef` (no digits) would print `Weak` instead.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- The input is a valid line of text with no leading or trailing spaces.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D11" t="n">

--- a/content/Question Bank/Coding Questions/Unit 12 - Exception Handling/Unit 12 - Exception Handling - Coding Questions.xlsx
+++ b/content/Question Bank/Coding Questions/Unit 12 - Exception Handling/Unit 12 - Exception Handling - Coding Questions.xlsx
@@ -7,10 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Set 1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Set 2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Set 3" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Set 4" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python - Coding - Unit 12" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -416,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH11"/>
+  <dimension ref="A1:AH41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -599,20 +596,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-After the semester party, Nikhil splits the total bill equally among his friends using a small program — but the one time he typed 0 friends by mistake, it crashed with an ugly error. Write a program that reads two whole numbers and prints the first divided by the second using integer division (//). If the second number is zero, catch the ZeroDivisionError and print 'Cannot divide by zero' instead of crashing.
-### Input Format
-- Line 1: First number
-- Line 2: Second number
-### Output Format
-```
-5
-```
+          <t>After the semester party, Nikhil splits the total bill equally among his friends using a small program — but the one time he typed 0 friends by mistake, it crashed with an ugly error. Write a program that reads two whole numbers and prints the first divided by the second using integer division (//). If the second number is zero, catch the ZeroDivisionError and print 'Cannot divide by zero' instead of crashing.
 ### Example Walkthrough
 Here the numbers are 10 and 2. Since 2 is not zero, no error is raised, and integer division 10 // 2 gives 5, so the program prints `5`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -755,7 +744,7 @@
 b = int(input())
 try:
     print(a // b)
-except ZeroDivisionError:
+except ZeroDivisionError:        # catches only this specific failure, not all errors
     print("Cannot divide by zero")</t>
         </is>
       </c>
@@ -768,20 +757,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-Priya keeps her cricket team's over-by-over runs in a list and lets teammates ask for the runs in any over by its position. Sometimes someone asks for a position that doesn't exist, and the program crashes. Write a program that reads a line of numbers and then an index (a position, counting from 0). Print the value at that index; if the index is too large, catch the IndexError and print 'Index out of range'.
-### Input Format
-- Line 1: Space-separated numbers
-- Line 2: An index
-### Output Format
-```
-20
-```
+          <t>Priya keeps her cricket team's over-by-over runs in a list and lets teammates ask for the runs in any over by its position. Sometimes someone asks for a position that doesn't exist, and the program crashes. Write a program that reads a line of numbers and then an index (a position, counting from 0). Print the value at that index; if the index is too large, catch the IndexError and print 'Index out of range'.
 ### Example Walkthrough
 The list is `10 20 30` and the index is 1. Counting from 0, position 1 holds the value 20, so no error occurs and the program prints `20`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -924,7 +905,7 @@
 i = int(input())
 try:
     print(nums[i])
-except IndexError:
+except IndexError:               # only catches an out-of-range index, not other bugs
     print("Index out of range")</t>
         </is>
       </c>
@@ -937,21 +918,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-The hostel office keeps a small lookup table: each line pairs a code (the key) with its value. When someone asks about a code that was never recorded, the program should answer politely instead of crashing. Write a program that reads N, then N 'key value' pairs into a dictionary, then one key. Using try/except around the dictionary lookup, print the value for that key, or 'Key not found' if it is missing.
-### Input Format
-- Line 1: N
-- Next N lines: 'key value'
-- Last line: a key
-### Output Format
-```
-1
-```
+          <t>The hostel office keeps a small lookup table: each line pairs a code (the key) with its value. When someone asks about a code that was never recorded, the program should answer politely instead of crashing. Write a program that reads N, then N 'key value' pairs into a dictionary, then one key. Using try/except around the dictionary lookup, print the value for that key, or 'Key not found' if it is missing.
 ### Example Walkthrough
 The two pairs are `a 1` and `b 2`, and the key asked for is `a`. The lookup finds `a` in the dictionary without raising a KeyError, so the program prints its value, `1`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -1108,7 +1080,7 @@
 query = input()
 try:
     print(data[query])
-except KeyError:
+except KeyError:                 # raised when the key is missing from the dict
     print("Key not found")</t>
         </is>
       </c>
@@ -1121,21 +1093,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-Sanya's physics lab program divides total distance by total time to compute speed, and the lab rules say every run must end with a 'Done' message in the record — whether the calculation worked or not. Write a program that reads two whole numbers and prints the first divided by the second; if the second is zero, print 'Cannot divide' instead. In both cases, print 'Done' at the end using a finally block, which always runs.
-### Input Format
-- Line 1: First number
-- Line 2: Second number
-### Output Format
-```
-5.0
-Done
-```
+          <t>Sanya's physics lab program divides total distance by total time to compute speed, and the lab rules say every run must end with a 'Done' message in the record — whether the calculation worked or not. Write a program that reads two whole numbers and prints the first divided by the second; if the second is zero, print 'Cannot divide' instead. In both cases, print 'Done' at the end using a finally block, which always runs.
 ### Example Walkthrough
 With 10 and 2, the division 10 / 2 succeeds and prints `5.0`. Then the finally block runs no matter what happened before, printing `Done` on the next line.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -1288,7 +1251,7 @@
 except ZeroDivisionError:
     print("Cannot divide")
 finally:
-    print("Done")</t>
+    print("Done")                # runs whether division succeeded or failed</t>
         </is>
       </c>
     </row>
@@ -1300,20 +1263,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-A mobile recharge kiosk lets customers type two amounts to divide, but people type all sorts of things — sometimes a zero, sometimes words instead of numbers. Write a program that reads two lines and divides the first by the second. Print 'Zero' if the second value is zero (a ZeroDivisionError), 'Invalid' if either value is not a number (a ValueError), and otherwise print the result.
-### Input Format
-- Line 1: First value
-- Line 2: Second value
-### Output Format
-```
-5.0
-```
+          <t>A mobile recharge kiosk lets customers type two amounts to divide, but people type all sorts of things — sometimes a zero, sometimes words instead of numbers. Write a program that reads two lines and divides the first by the second. Print 'Zero' if the second value is zero (a ZeroDivisionError), 'Invalid' if either value is not a number (a ValueError), and otherwise print the result.
 ### Example Walkthrough
 Both sample inputs, 10 and 2, convert to numbers without trouble, and 2 is not zero — so neither error occurs, and the program prints 10 / 2, which is `5.0`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -1456,9 +1411,9 @@
     a = int(input())
     b = int(input())
     print(a / b)
-except ZeroDivisionError:
+except ZeroDivisionError:        # b was zero
     print("Zero")
-except ValueError:
+except ValueError:               # input wasn't a valid integer
     print("Invalid")</t>
         </is>
       </c>
@@ -1471,19 +1426,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-Volunteers signing people up for the college blood-donation camp must record a sensible age — typos like -5 or 200 have slipped through before. Write a program that reads an age and raises a ValueError yourself (using `raise`) if the age is below 0 or above 150. Catch that error and print 'Invalid age'; if no error is raised, print 'Valid age'.
-### Input Format
-- Line 1: An age
-### Output Format
-```
-Valid age
-```
+          <t>Volunteers signing people up for the college blood-donation camp must record a sensible age — typos like -5 or 200 have slipped through before. Write a program that reads an age and raises a ValueError yourself (using `raise`) if the age is below 0 or above 150. Catch that error and print 'Invalid age'; if no error is raised, print 'Valid age'.
 ### Example Walkthrough
 The sample age is 25, which sits comfortably between 0 and 150. No ValueError is raised, the except block is skipped, and the program prints `Valid age`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1618,7 +1566,7 @@
           <t>age = int(input())
 try:
     if age &lt; 0 or age &gt; 150:
-        raise ValueError("bad age")
+        raise ValueError("bad age")   # manually flag an unrealistic age as invalid
     print("Valid age")
 except ValueError:
     print("Invalid age")</t>
@@ -1633,20 +1581,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-During internal exam moderation, every mark awarded must fall between a minimum and a maximum set by the department, and Ishan is writing the checker. Write a program that reads a value, then a line containing the minimum and maximum. Raise a ValueError when the value falls outside the range, catch it, and print 'Out of range'; if the value is between them (inclusive), print 'In range'.
-### Input Format
-- Line 1: The value
-- Line 2: 'min max'
-### Output Format
-```
-In range
-```
+          <t>During internal exam moderation, every mark awarded must fall between a minimum and a maximum set by the department, and Ishan is writing the checker. Write a program that reads a value, then a line containing the minimum and maximum. Raise a ValueError when the value falls outside the range, catch it, and print 'Out of range'; if the value is between them (inclusive), print 'In range'.
 ### Example Walkthrough
 The value is 5 and the allowed range is 1 to 10. Since 1 &lt;= 5 &lt;= 10, no error is raised, so the program prints `In range`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1789,7 +1729,7 @@
 low, high = map(int, input().split())
 try:
     if not (low &lt;= value &lt;= high):
-        raise ValueError()
+        raise ValueError()       # value is outside the allowed range
     print("In range")
 except ValueError:
     print("Out of range")</t>
@@ -1804,22 +1744,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-The campus canteen smart card works like a tiny bank: students deposit money and withdraw it to pay for meals, but the card must never go below zero. Write a program that defines a custom exception class named InsufficientFunds. Read a starting balance and N operations, each 'deposit X' or 'withdraw X'. A withdrawal larger than the current balance raises InsufficientFunds — catch it and print 'Insufficient funds' (the balance stays unchanged). After each successful operation, print the new balance.
-### Input Format
-- Line 1: Starting balance
-- Line 2: N
-- Next N lines: 'deposit X' or 'withdraw X'
-### Output Format
-```
-50
-Insufficient funds
-```
+          <t>The campus canteen smart card works like a tiny bank: students deposit money and withdraw it to pay for meals, but the card must never go below zero. Write a program that defines a custom exception class named InsufficientFunds. Read a starting balance and N operations, each 'deposit X' or 'withdraw X'. A withdrawal larger than the current balance raises InsufficientFunds — catch it and print 'Insufficient funds' (the balance stays unchanged). After each successful operation, print the new balance.
 ### Example Walkthrough
 Starting at 100, `withdraw 50` succeeds and the new balance `50` is printed. Then `withdraw 100` asks for more than the remaining 50, so InsufficientFunds is raised and the program prints `Insufficient funds`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1966,7 +1896,7 @@
       <c r="AG9" t="inlineStr">
         <is>
           <t>class InsufficientFunds(Exception):
-    pass
+    pass    # a distinct exception type makes this failure easy to catch specifically
 balance = int(input())
 n = int(input())
 for _ in range(n):
@@ -1975,7 +1905,7 @@
     try:
         if op == "withdraw":
             if amount &gt; balance:
-                raise InsufficientFunds()
+                raise InsufficientFunds()   # signal the withdrawal can't be completed
             balance -= amount
         else:
             balance += amount
@@ -1995,17 +1925,11 @@
         <is>
           <t>A quiz app reads a player's numeric answer from a text box, but sometimes players type letters by mistake instead of a number; the app must catch that mistake instead of crashing.
 Write a program that reads a line of input inside a `try` block, converts it to an integer, and prints it. If the conversion raises a `ValueError` (the text isn't a valid whole number), catch it and print `Invalid` instead.
-### Input Format
-- Line 1: A value that may or may not be a whole number
-### Output Format
-```
-10
-```
 ### Example Walkthrough
 In the sample, the input is `10`, which converts to an integer without error, so the program prints `10`. An input like `abc` would raise a `ValueError` and print `Invalid` instead.
 ### Constraints
 - The input is a single line of text.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -2139,7 +2063,7 @@
         <is>
           <t>try:
  print(int(input()))
-except ValueError: print("Invalid")</t>
+except ValueError: print("Invalid")   # input wasn't a valid integer</t>
         </is>
       </c>
     </row>
@@ -2153,18 +2077,11 @@
         <is>
           <t>A playlist app lets a user jump to a song by its position number, but the number they type might be out of range or not a number at all, so the app needs to catch both kinds of mistakes gracefully instead of crashing.
 Write a program that reads a line of space-separated items into a list, then reads a position, and prints the item at that position (a negative position is valid and counts from the end, as in normal Python indexing). If the position is not a valid whole number, or is out of range, catch the error and print `Error`.
-### Input Format
-- Line 1: Space-separated items
-- Line 2: A position
-### Output Format
-```
-b
-```
 ### Example Walkthrough
 In the sample, the items are `a b c` and the position is `1`. The item at position 1 is `b`, so the program prints `b`. A position of `5` (out of range) would print `Error` instead.
 ### Constraints
 - The items line is a valid, non-empty line of space-separated values.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -2305,551 +2222,347 @@
         <is>
           <t>items=input().split()
 try: print(items[int(input())])
-except (ValueError,IndexError): print("Error")</t>
+except (ValueError,IndexError): print("Error")   # catches bad index text or out-of-range index</t>
         </is>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AH11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>explanation</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>score</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>difficulty</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>bloomTaxonomy</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>tags</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>subjects</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>topics</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>subTopics</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>companies</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>codingType</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>language</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>supportAllLanguages</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>enablePartialScore</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>ignoreCase</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>testcase1_input</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>testcase1_output</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>testcase2_input</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>testcase2_output</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>testcase3_input</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>testcase3_output</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>testcase4_input</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>testcase4_output</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>testcase5_input</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>testcase5_output</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>testcase6_input</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>testcase6_output</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>testcase7_input</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>testcase7_output</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>preloadCode_python</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>solution_python</t>
-        </is>
-      </c>
-      <c r="AH1" t="inlineStr">
-        <is>
-          <t>hints</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>Python - Validate Registration</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-Registrations for the inter-college hackathon are pouring in, and Anu must reject badly filled forms with a clear reason. Write a program that reads a name, an age, and an email, and checks them in order: the name must not be empty, the age must be a whole number from 1 to 120, and the email must contain '@'. Print 'Valid' if all three checks pass; otherwise print only the first failure: 'Invalid name', 'Invalid age', or 'Invalid email'.
-### Input Format
-- Line 1: Name
-- Line 2: Age
-- Line 3: Email
-### Output Format
-```
-Valid
-```
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Registrations for the inter-college hackathon are pouring in, and Anu must reject badly filled forms with a clear reason. Write a program that reads a name, an age, and an email, and checks them in order: the name must not be empty, the age must be a whole number from 1 to 120, and the email must contain '@'. Print 'Valid' if all three checks pass; otherwise print only the first failure: 'Invalid name', 'Invalid age', or 'Invalid email'.
 ### Example Walkthrough
 The sample form has the name `Asha` (not empty), the age 20 (a whole number between 1 and 120), and the email `asha@x.com` (contains '@'). All three checks pass, so the program prints `Valid`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
         <v>5</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>exception-handling</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>raising-exceptions</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O2" t="b">
+      <c r="O12" t="b">
         <v>0</v>
       </c>
-      <c r="P2" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q2" t="b">
-        <v>1</v>
-      </c>
-      <c r="R2" t="inlineStr">
+      <c r="P12" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q12" t="b">
+        <v>1</v>
+      </c>
+      <c r="R12" t="inlineStr">
         <is>
           <t>Asha
 20
 asha@x.com</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>Valid</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Bob
 200
 b@x.com</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>Invalid age</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>Sam
 25
 samx.com</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>Invalid email</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t xml:space="preserve">
 20
 a@x.com</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>Invalid name</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="Z12" t="inlineStr">
         <is>
           <t>Meera
 abc
 m@x.com</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>Invalid age</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>Zed
 0
 z@x.com</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>Invalid age</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AD12" t="inlineStr">
         <is>
           <t>Kabir
 120
 k@x.com</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AE12" t="inlineStr">
         <is>
           <t>Valid</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AG12" t="inlineStr">
         <is>
           <t>name = input()
 age_text = input()
 email = input()
 try:
     if name.strip() == "":
-        raise ValueError("Invalid name")
+        raise ValueError("Invalid name")     # empty name fails validation
     try:
         age = int(age_text)
     except ValueError:
-        raise ValueError("Invalid age")
+        raise ValueError("Invalid age")      # re-raise as a validation error with a clear message
     if not (1 &lt;= age &lt;= 120):
         raise ValueError("Invalid age")
     if "@" not in email:
         raise ValueError("Invalid email")
     print("Valid")
 except ValueError as e:
-    print(e)</t>
+    print(e)                                  # print whichever validation message was raised</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Python - Calculator with Errors</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-Uncle Prakash's stationery shop runs a small calculator program at the billing counter, and it must never crash mid-billing no matter what gets typed. Write a program that reads a number, an operator (+, -, *, or /), and a second number, then prints the result of applying the operator. If the customer tries to divide by zero, print 'Cannot divide by zero'; if the operator is not one of the four, print 'Unknown operator'.
-### Input Format
-- Line 1: First number
-- Line 2: Operator
-- Line 3: Second number
-### Output Format
-```
-Cannot divide by zero
-```
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Uncle Prakash's stationery shop runs a small calculator program at the billing counter, and it must never crash mid-billing no matter what gets typed. Write a program that reads a number, an operator (+, -, *, or /), and a second number, then prints the result of applying the operator. If the customer tries to divide by zero, print 'Cannot divide by zero'; if the operator is not one of the four, print 'Unknown operator'.
 ### Example Walkthrough
 The sample inputs are 6, `/`, and 0. Dividing 6 by 0 raises a ZeroDivisionError, which the program catches instead of crashing, so it prints `Cannot divide by zero`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
         <v>5</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>exception-handling</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>exception-handling-patterns</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O3" t="b">
+      <c r="O13" t="b">
         <v>0</v>
       </c>
-      <c r="P3" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q3" t="b">
-        <v>1</v>
-      </c>
-      <c r="R3" t="inlineStr">
+      <c r="P13" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q13" t="b">
+        <v>1</v>
+      </c>
+      <c r="R13" t="inlineStr">
         <is>
           <t>6
 /
 0</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>Cannot divide by zero</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>5
 %
 2</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>Unknown operator</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>10
 +
 5</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>0
 *
 5</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Y13" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="Z13" t="inlineStr">
         <is>
           <t>-6
 -
 2</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AA13" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AB13" t="inlineStr">
         <is>
           <t>7
 /
 2</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AC13" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AD13" t="inlineStr">
         <is>
           <t>10
 ^
 3</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AE13" t="inlineStr">
         <is>
           <t>Unknown operator</t>
         </is>
       </c>
-      <c r="AG3" t="inlineStr">
+      <c r="AG13" t="inlineStr">
         <is>
           <t>a = int(input())
 op = input()
@@ -2864,7 +2577,7 @@
     elif op == "/":
         print(a // b)
     else:
-        raise ValueError("Unknown operator")
+        raise ValueError("Unknown operator")   # operator wasn't one of the supported ones
 except ZeroDivisionError:
     print("Cannot divide by zero")
 except ValueError as e:
@@ -2872,1101 +2585,1061 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>Python - Safe Integer</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Read a line and try to treat it as a whole number, printing double its value. If it is not a valid number, print 'Not a number'.
-### Input Format
-- Line 1: A value
-### Output Format
-```
-10
-```
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>A campus event's signup form offers a welcome bonus: whatever number of points a new member types into the referral box gets doubled as a joining gift. But the field is free text, and not everyone types a clean number.
+Write a program that reads the entered value and tries to convert it into a whole number, printing double that value. If the entry is not a valid whole number, print 'Not a number'.
 ### Example Walkthrough
 In the sample, the input is `5`. It converts to an integer cleanly, and doubling it gives `10`, so the program prints `10`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
         <v>5</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>exception-handling</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>try-except</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O4" t="b">
+      <c r="O14" t="b">
         <v>0</v>
       </c>
-      <c r="P4" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q4" t="b">
-        <v>1</v>
-      </c>
-      <c r="R4" t="inlineStr">
+      <c r="P14" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q14" t="b">
+        <v>1</v>
+      </c>
+      <c r="R14" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>abc</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>Not a number</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>-6</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="Y14" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="Z14" t="inlineStr">
         <is>
           <t>3.5</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AA14" t="inlineStr">
         <is>
           <t>Not a number</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AB14" t="inlineStr">
         <is>
           <t xml:space="preserve">
 </t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AC14" t="inlineStr">
         <is>
           <t>Not a number</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AD14" t="inlineStr">
         <is>
           <t>999999</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
+      <c r="AE14" t="inlineStr">
         <is>
           <t>1999998</t>
         </is>
       </c>
-      <c r="AG4" t="inlineStr">
+      <c r="AG14" t="inlineStr">
         <is>
           <t>text = input()
 try:
     print(int(text) * 2)
-except ValueError:
+except ValueError:                # text wasn't a valid whole number
     print("Not a number")</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>Python - Safe Float</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Read a line and try to treat it as a decimal number, printing it rounded to 2 decimal places. If it is not valid, print 'Invalid'.
-### Input Format
-- Line 1: A value
-### Output Format
-```
-3.14
-```
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>The same signup form also asks each student for their current CGPA, which should be a decimal number. Since students type this in freely, the app needs to validate it and round it to a fixed precision before storing it.
+Read a line and try to treat it as a decimal number, printing it rounded to 2 decimal places. If it is not a valid decimal number, print 'Invalid'.
 ### Example Walkthrough
 In the sample, the input is `3.14`. It converts to a float cleanly, and rounding to 2 decimal places leaves it as `3.14`, so the program prints `3.14`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
         <v>5</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>exception-handling</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>try-except</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O5" t="b">
+      <c r="O15" t="b">
         <v>0</v>
       </c>
-      <c r="P5" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q5" t="b">
-        <v>1</v>
-      </c>
-      <c r="R5" t="inlineStr">
+      <c r="P15" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q15" t="b">
+        <v>1</v>
+      </c>
+      <c r="R15" t="inlineStr">
         <is>
           <t>3.14159</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>3.14</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>hello</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>Invalid</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="Y15" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="Z15" t="inlineStr">
         <is>
           <t>-1.005</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AA15" t="inlineStr">
         <is>
           <t>-1.0</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AB15" t="inlineStr">
         <is>
           <t xml:space="preserve">
 </t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AC15" t="inlineStr">
         <is>
           <t>Invalid</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AD15" t="inlineStr">
         <is>
           <t>1e10</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
+      <c r="AE15" t="inlineStr">
         <is>
           <t>10000000000.0</t>
         </is>
       </c>
-      <c r="AG5" t="inlineStr">
+      <c r="AG15" t="inlineStr">
         <is>
           <t>text = input()
 try:
     print(round(float(text), 2))
-except ValueError:
+except ValueError:                # text wasn't a valid decimal number
     print("Invalid")</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Python - Add Two Safely</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Read two lines and print their sum as whole numbers. If either line is not a valid number, print 'Invalid input'.
-### Input Format
-- Line 1: First value
-- Line 2: Second value
-### Output Format
-```
-7
-```
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>A simple calculator app lets a user add two numbers entered in separate boxes, but since the boxes are plain text fields, a user could type letters into one by mistake.
+Read two lines and print their sum as whole numbers. If either line is not a valid whole number, print 'Invalid input'.
 ### Example Walkthrough
 In the sample, the values are `3` and `4`. Both convert cleanly, and adding them gives `7`, so the program prints `7`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
         <v>5</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>exception-handling</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>try-except</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O6" t="b">
+      <c r="O16" t="b">
         <v>0</v>
       </c>
-      <c r="P6" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q6" t="b">
-        <v>1</v>
-      </c>
-      <c r="R6" t="inlineStr">
+      <c r="P16" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q16" t="b">
+        <v>1</v>
+      </c>
+      <c r="R16" t="inlineStr">
         <is>
           <t>3
 4</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>x
 5</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>Invalid input</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>10
 20</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>0
 0</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="Y16" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="Z16" t="inlineStr">
         <is>
           <t>-5
 5</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AA16" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AB16" t="inlineStr">
         <is>
           <t>7
 y</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AC16" t="inlineStr">
         <is>
           <t>Invalid input</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AD16" t="inlineStr">
         <is>
           <t>100
 200</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AE16" t="inlineStr">
         <is>
           <t>300</t>
         </is>
       </c>
-      <c r="AG6" t="inlineStr">
+      <c r="AG16" t="inlineStr">
         <is>
           <t>try:
     a = int(input())
     b = int(input())
     print(a + b)
-except ValueError:
+except ValueError:                # either line wasn't a valid integer
     print("Invalid input")</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>Python - Sum Valid Numbers</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Read a line of tokens separated by spaces and print the sum of only the ones that are valid whole numbers, ignoring the rest.
-### Input Format
-- Line 1: Space-separated tokens
-### Output Format
-```
-6
-```
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>The same calculator app has a quick-sum shortcut: a user pastes a line of space-separated numbers copied from a notes app, but stray words sometimes get mixed in with the numbers.
+Read a line of tokens separated by spaces and print the sum of only the ones that are valid whole numbers, ignoring the rest.
 ### Example Walkthrough
 In the sample, the tokens are `1 two 2 three 3`. Only `1`, `2`, and `3` are valid numbers, and they sum to `6`, so the program prints `6`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
         <v>5</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>exception-handling</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>try-except</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O7" t="b">
+      <c r="O17" t="b">
         <v>0</v>
       </c>
-      <c r="P7" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q7" t="b">
-        <v>1</v>
-      </c>
-      <c r="R7" t="inlineStr">
+      <c r="P17" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q17" t="b">
+        <v>1</v>
+      </c>
+      <c r="R17" t="inlineStr">
         <is>
           <t>1 2 x 3</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>a b</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>10 20 hi 30</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="Y17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="Z17" t="inlineStr">
         <is>
           <t>-1 -2 3</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AA17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AB17" t="inlineStr">
         <is>
           <t>1 2 3 4</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AC17" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AD17" t="inlineStr">
         <is>
           <t>x y z</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AE17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AG7" t="inlineStr">
+      <c r="AG17" t="inlineStr">
         <is>
           <t>total = 0
 for token in input().split():
     try:
         total += int(token)
-    except ValueError:
+    except ValueError:            # skip tokens that aren't valid numbers
         pass
 print(total)</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>Python - Safe Modulo</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Read two whole numbers and print the remainder of the first divided by the second. If the second is zero, print 'Cannot mod by zero'.
-### Input Format
-- Line 1: First number
-- Line 2: Second number
-### Output Format
-```
-1
-```
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>The calculator app also has a 'remainder' button, handy for splitting tasks evenly among a group, but a careless tap could leave the group size set to zero.
+Read two whole numbers and print the remainder of the first divided by the second. If the second number is zero, print 'Cannot mod by zero'.
 ### Example Walkthrough
 In the sample, the numbers are `7` and `3`. Since `7 % 3 = 1`, the program prints `1`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
         <v>5</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>exception-handling</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>try-except</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O8" t="b">
+      <c r="O18" t="b">
         <v>0</v>
       </c>
-      <c r="P8" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q8" t="b">
-        <v>1</v>
-      </c>
-      <c r="R8" t="inlineStr">
+      <c r="P18" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q18" t="b">
+        <v>1</v>
+      </c>
+      <c r="R18" t="inlineStr">
         <is>
           <t>10
 3</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>5
 0</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>Cannot mod by zero</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>8
 4</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>0
 5</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="Y18" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="Z18" t="inlineStr">
         <is>
           <t>-10
 3</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AA18" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AB18" t="inlineStr">
         <is>
           <t>1
 1</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AC18" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AD18" t="inlineStr">
         <is>
           <t>-8
 0</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AE18" t="inlineStr">
         <is>
           <t>Cannot mod by zero</t>
         </is>
       </c>
-      <c r="AG8" t="inlineStr">
+      <c r="AG18" t="inlineStr">
         <is>
           <t>a = int(input())
 b = int(input())
 try:
     print(a % b)
-except ZeroDivisionError:
+except ZeroDivisionError:         # b was zero
     print("Cannot mod by zero")</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Python - Safe Square Root</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Read a number and print its square root. If the number is negative, the square root fails, so catch the error and print 'Cannot take square root of negative'.
-### Input Format
-- Line 1: A number
-### Output Format
-```
-4.0
-```
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Another button on the calculator computes square roots, but Python's math.sqrt refuses to work on a negative number and raises an error instead.
+Read a number and print its square root. If the number is negative, catch the resulting error and print 'Cannot take square root of negative'.
 ### Example Walkthrough
 In the sample, the number is `16`. Its square root is `4.0`, so the program prints `4.0`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
         <v>5</v>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>exception-handling</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>try-except</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O9" t="b">
+      <c r="O19" t="b">
         <v>0</v>
       </c>
-      <c r="P9" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q9" t="b">
-        <v>1</v>
-      </c>
-      <c r="R9" t="inlineStr">
+      <c r="P19" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q19" t="b">
+        <v>1</v>
+      </c>
+      <c r="R19" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>Cannot take square root of negative</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="Y19" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="Z19" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AA19" t="inlineStr">
         <is>
           <t>Cannot take square root of negative</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AB19" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AC19" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AD19" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AE19" t="inlineStr">
         <is>
           <t>10.0</t>
         </is>
       </c>
-      <c r="AG9" t="inlineStr">
+      <c r="AG19" t="inlineStr">
         <is>
           <t>import math
 n = int(input())
 try:
     print(math.sqrt(n))
-except ValueError:
+except ValueError:                # sqrt of a negative number raises ValueError
     print("Cannot take square root of negative")</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>Python - Safe Key Lookup</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>A student ID lookup kiosk stores registered names mapped to their ID numbers; if someone types a name that was never registered, the kiosk should report it as missing instead of crashing.
 Write a program that reads a whole number N, then reads N lines each with a name and an ID separated by a space and stores them in a dictionary, then reads one more name and prints its ID. If the name is not in the dictionary, catch the `KeyError` and print `Missing` instead.
-### Input Format
-- Line 1: N, the number of registered names
-- Next N lines: name and ID separated by a space
-- Final line: the name being looked up
-### Output Format
-```
-10
-```
 ### Example Walkthrough
 In the sample, N is 1 with `a 10` registered, and the query is `a`. Since `a` is in the dictionary with ID `10`, the program prints `10`. A query for an unregistered name would print `Missing` instead.
 ### Constraints
 - Names and IDs are valid strings with no spaces within them.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
         <v>5</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>exception-handling</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>try-except</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O10" t="b">
+      <c r="O20" t="b">
         <v>0</v>
       </c>
-      <c r="P10" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q10" t="b">
-        <v>1</v>
-      </c>
-      <c r="R10" t="inlineStr">
+      <c r="P20" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q20" t="b">
+        <v>1</v>
+      </c>
+      <c r="R20" t="inlineStr">
         <is>
           <t>1
 a 10
 a</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>1
 a 10
 b</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>0
 x</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>2
 x 1
@@ -3974,12 +3647,12 @@
 y</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="Y20" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="Z20" t="inlineStr">
         <is>
           <t>2
 x 1
@@ -3987,563 +3660,363 @@
 z</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AA20" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AB20" t="inlineStr">
         <is>
           <t>1
 name Asha
 name</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AC20" t="inlineStr">
         <is>
           <t>Asha</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AD20" t="inlineStr">
         <is>
           <t>1
 name Asha
 age</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AE20" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="AG10" t="inlineStr">
+      <c r="AG20" t="inlineStr">
         <is>
           <t>n=int(input()); d={}
 for _ in range(n):
  k,v=input().split(); d[k]=v
 try: print(d[input()])
-except KeyError: print("Missing")</t>
+except KeyError: print("Missing")   # name was never registered in the dict</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>Python - Finally Message</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>A device-connection routine always needs to print a closing status message, whether the connection attempt succeeded or failed, so the cleanup step is written inside a `finally` block that runs no matter what happens.
 Write a program that reads a line inside a `try` block, converts it to an integer, and prints it; if conversion raises a `ValueError`, catch it and print `Invalid` instead. Either way, use a `finally` block to print `Done` as the last line.
-### Input Format
-- Line 1: A value that may or may not be a whole number
-### Output Format
-```
-5
-Done
-```
 ### Example Walkthrough
 In the sample, the input is `5`, which converts successfully and prints `5`, and then the `finally` block always runs and prints `Done`. An input like `x` would print `Invalid` followed by `Done`.
 ### Constraints
 - The input is a single line of text.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
         <v>5</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>exception-handling</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>exception-handling-patterns</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O11" t="b">
+      <c r="O21" t="b">
         <v>0</v>
       </c>
-      <c r="P11" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q11" t="b">
-        <v>1</v>
-      </c>
-      <c r="R11" t="inlineStr">
+      <c r="P21" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q21" t="b">
+        <v>1</v>
+      </c>
+      <c r="R21" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>5
 Done</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>Invalid
 Done</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>0
 Done</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="Y21" t="inlineStr">
         <is>
           <t>-1
 Done</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="Z21" t="inlineStr">
         <is>
           <t>3.5</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AA21" t="inlineStr">
         <is>
           <t>Invalid
 Done</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AB21" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AC21" t="inlineStr">
         <is>
           <t>100
 Done</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AD21" t="inlineStr">
         <is>
           <t>abc</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
+      <c r="AE21" t="inlineStr">
         <is>
           <t>Invalid
 Done</t>
         </is>
       </c>
-      <c r="AG11" t="inlineStr">
+      <c r="AG21" t="inlineStr">
         <is>
           <t>try: print(int(input()))
 except ValueError: print("Invalid")
-finally: print("Done")</t>
+finally: print("Done")   # always runs, whether conversion succeeded or failed</t>
         </is>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AH11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>explanation</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>score</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>difficulty</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>bloomTaxonomy</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>tags</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>subjects</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>topics</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>subTopics</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>companies</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>codingType</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>language</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>supportAllLanguages</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>enablePartialScore</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>ignoreCase</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>testcase1_input</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>testcase1_output</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>testcase2_input</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>testcase2_output</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>testcase3_input</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>testcase3_output</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>testcase4_input</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>testcase4_output</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>testcase5_input</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>testcase5_output</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>testcase6_input</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>testcase6_output</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>testcase7_input</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>testcase7_output</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>preloadCode_python</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>solution_python</t>
-        </is>
-      </c>
-      <c r="AH1" t="inlineStr">
-        <is>
-          <t>hints</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Python - Else and Finally</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Read two numbers and divide them. Use an else block to print the result when it works, an except block to print 'Error' on divide-by-zero, and a finally block that always prints 'Checked'.
-### Input Format
-- Line 1: First number
-- Line 2: Second number
-### Output Format
-```
-4.0
-Checked
-```
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>A data-import tool divides two numbers pulled from a spreadsheet row as part of a sanity check, and it needs to log whether the division succeeded while always recording that the row was checked, no matter the outcome.
+Read two numbers and divide them. Use an else block to print the result when the division works, an except block to print 'Error' on divide-by-zero, and a finally block that always prints 'Checked'.
 ### Example Walkthrough
 In the sample, the numbers are `8` and `2`. Dividing them gives `4.0`, printed by the else block, and the finally block always runs afterward, printing `Checked`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
         <v>5</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>exception-handling</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>try-except</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O2" t="b">
+      <c r="O22" t="b">
         <v>0</v>
       </c>
-      <c r="P2" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q2" t="b">
-        <v>1</v>
-      </c>
-      <c r="R2" t="inlineStr">
+      <c r="P22" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q22" t="b">
+        <v>1</v>
+      </c>
+      <c r="R22" t="inlineStr">
         <is>
           <t>8
 2</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="S22" t="inlineStr">
         <is>
           <t>4.0
 Checked</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="T22" t="inlineStr">
         <is>
           <t>9
 0</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="U22" t="inlineStr">
         <is>
           <t>Error
 Checked</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="V22" t="inlineStr">
         <is>
           <t>10
 5</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>2.0
 Checked</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="X22" t="inlineStr">
         <is>
           <t>0
 5</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="Y22" t="inlineStr">
         <is>
           <t>0.0
 Checked</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="Z22" t="inlineStr">
         <is>
           <t>-8
 2</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AA22" t="inlineStr">
         <is>
           <t>-4.0
 Checked</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AB22" t="inlineStr">
         <is>
           <t>1
 1</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AC22" t="inlineStr">
         <is>
           <t>1.0
 Checked</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AD22" t="inlineStr">
         <is>
           <t>-9
 0</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AE22" t="inlineStr">
         <is>
           <t>Error
 Checked</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AG22" t="inlineStr">
         <is>
           <t>a = int(input())
 b = int(input())
@@ -4552,256 +4025,245 @@
 except ZeroDivisionError:
     print("Error")
 else:
-    print(result)
+    print(result)          # runs only when the try block succeeded, no exception raised
 finally:
-    print("Checked")</t>
+    print("Checked")       # always runs, success or failure</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>Python - Custom Exception</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Define a custom exception called NegativeError. Read a number and raise NegativeError if it is negative; catch it and print 'Negative not allowed'. Otherwise print the number's square.
-### Input Format
-- Line 1: A number
-### Output Format
-```
-25
-```
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>A banking app's internal fraud-checker computes a risk score for each transaction by squaring the transaction amount, since larger swings should produce a much larger score. A transaction amount should never be negative, so the app defines a custom exception called NegativeError to flag one immediately instead of letting it slip through.
+Define a custom exception called NegativeError. Read a number and raise NegativeError if it is negative; catch it and print 'Negative not allowed'. Otherwise print the number's square.
 ### Example Walkthrough
 In the sample, the number is `5`, which is not negative, so `NegativeError` is never raised, and the program prints its square, `25`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
         <v>5</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>exception-handling</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>custom-exceptions</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O3" t="b">
+      <c r="O23" t="b">
         <v>0</v>
       </c>
-      <c r="P3" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q3" t="b">
-        <v>1</v>
-      </c>
-      <c r="R3" t="inlineStr">
+      <c r="P23" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q23" t="b">
+        <v>1</v>
+      </c>
+      <c r="R23" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="S23" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="T23" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="U23" t="inlineStr">
         <is>
           <t>Negative not allowed</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="V23" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="W23" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="X23" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Y23" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="Z23" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AA23" t="inlineStr">
         <is>
           <t>Negative not allowed</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AB23" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AC23" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AD23" t="inlineStr">
         <is>
           <t>-100</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AE23" t="inlineStr">
         <is>
           <t>Negative not allowed</t>
         </is>
       </c>
-      <c r="AG3" t="inlineStr">
+      <c r="AG23" t="inlineStr">
         <is>
           <t>class NegativeError(Exception):
-    pass
+    pass    # a distinct exception type makes this failure easy to catch specifically
 n = int(input())
 try:
     if n &lt; 0:
-        raise NegativeError()
+        raise NegativeError()   # signal that a negative number isn't allowed here
     print(n * n)
 except NegativeError:
     print("Negative not allowed")</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>Python - First Valid Number</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Read N lines and print the first one that is a valid whole number. If none of them are, print 'No valid number'.
-### Input Format
-- Line 1: N
-- Next N lines: values
-### Output Format
-```
-12
-```
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>A quiz app's answer box lets a student make several attempts on separate lines if they mistype their response, and the app should accept the very first attempt that turns out to be a valid whole number.
+Read N lines and print the first one that is a valid whole number. If none of the N lines are valid, print 'No valid number'.
 ### Example Walkthrough
 In the sample, `N` is `3` with the lines `abc`, `12`, and `34`. The first line that converts successfully is `12`, so the program prints `12`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
         <v>5</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>exception-handling</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>exception-handling-patterns</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O4" t="b">
+      <c r="O24" t="b">
         <v>0</v>
       </c>
-      <c r="P4" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q4" t="b">
-        <v>1</v>
-      </c>
-      <c r="R4" t="inlineStr">
+      <c r="P24" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q24" t="b">
+        <v>1</v>
+      </c>
+      <c r="R24" t="inlineStr">
         <is>
           <t>3
 abc
@@ -4809,57 +4271,57 @@
 xyz</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="S24" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="T24" t="inlineStr">
         <is>
           <t>2
 x
 y</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="U24" t="inlineStr">
         <is>
           <t>No valid number</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="V24" t="inlineStr">
         <is>
           <t>2
 5
 6</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="W24" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="X24" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="Y24" t="inlineStr">
         <is>
           <t>No valid number</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="Z24" t="inlineStr">
         <is>
           <t>1
 abc</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AA24" t="inlineStr">
         <is>
           <t>No valid number</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AB24" t="inlineStr">
         <is>
           <t>3
 x
@@ -4867,12 +4329,12 @@
 0</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AC24" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AD24" t="inlineStr">
         <is>
           <t>4
 a
@@ -4881,12 +4343,12 @@
 -5</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
+      <c r="AE24" t="inlineStr">
         <is>
           <t>-5</t>
         </is>
       </c>
-      <c r="AG4" t="inlineStr">
+      <c r="AG24" t="inlineStr">
         <is>
           <t>n = int(input())
 answer = "No valid number"
@@ -4894,589 +4356,566 @@
     line = input()
     try:
         answer = int(line)
-        break
+        break               # stop at the first successful conversion
     except ValueError:
-        continue
+        continue            # skip this line and try the next one
 print(answer)</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Python - Safe Nested Lookup</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Read a line of JSON and print the value at data['user']['name']. If any part of that path is missing, print 'Not available'.
-### Input Format
-- Line 1: A JSON object
-### Output Format
-```
-Asha
-```
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>A survey app stores each respondent's answers as nested JSON, and a report generator needs to pull the respondent's name out of data['user']['name'], but some records are missing pieces of that structure.
+Read a line of JSON and print the value at data['user']['name']. If any part of that path is missing, print 'Not available'.
 ### Example Walkthrough
 In the sample, the JSON is `{"user": {"name": "Asha"}}`. Both keys exist, so the program prints `Asha`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
         <v>5</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>exception-handling</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>try-except</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O5" t="b">
+      <c r="O25" t="b">
         <v>0</v>
       </c>
-      <c r="P5" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q5" t="b">
-        <v>1</v>
-      </c>
-      <c r="R5" t="inlineStr">
+      <c r="P25" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q25" t="b">
+        <v>1</v>
+      </c>
+      <c r="R25" t="inlineStr">
         <is>
           <t>{"user": {"name": "Asha"}}</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="S25" t="inlineStr">
         <is>
           <t>Asha</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="T25" t="inlineStr">
         <is>
           <t>{"user": {}}</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="U25" t="inlineStr">
         <is>
           <t>Not available</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="V25" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="W25" t="inlineStr">
         <is>
           <t>Not available</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="X25" t="inlineStr">
         <is>
           <t>{"user": {"name": ""}}</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="Z25" t="inlineStr">
         <is>
           <t>{"other": 1}</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AA25" t="inlineStr">
         <is>
           <t>Not available</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AB25" t="inlineStr">
         <is>
           <t>{"user": {"name": "Kabir", "age": 20}}</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AC25" t="inlineStr">
         <is>
           <t>Kabir</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AD25" t="inlineStr">
         <is>
           <t>{"x": 1, "y": 2}</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
+      <c r="AE25" t="inlineStr">
         <is>
           <t>Not available</t>
         </is>
       </c>
-      <c r="AG5" t="inlineStr">
+      <c r="AG25" t="inlineStr">
         <is>
           <t>import json
 data = json.loads(input())
 try:
     print(data["user"]["name"])
-except KeyError:
+except KeyError:            # a required key is missing somewhere in the path
     print("Not available")</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>Python - Index or Bad Input</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Read a line of numbers and an index. Print the value at that index, 'Invalid index' if the index is not a number, or 'Out of range' if it is too large.
-### Input Format
-- Line 1: Space-separated numbers
-- Line 2: An index
-### Output Format
-```
-20
-```
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>A warehouse inventory tool keeps stock counts in a list, and a staff member can type in a shelf index to check the quantity there, but the typed index might not be a number at all, or might point past the end of the shelf.
+Read a line of numbers and an index. Print the value at that index, 'Invalid index' if the index is not a number, or 'Out of range' if the index is too large.
 ### Example Walkthrough
 In the sample, the numbers are `10 20 30` and the index is `1`. Position `1` holds `20`, so the program prints `20`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
         <v>5</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>exception-handling</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>exception-handling-patterns</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O6" t="b">
+      <c r="O26" t="b">
         <v>0</v>
       </c>
-      <c r="P6" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q6" t="b">
-        <v>1</v>
-      </c>
-      <c r="R6" t="inlineStr">
+      <c r="P26" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q26" t="b">
+        <v>1</v>
+      </c>
+      <c r="R26" t="inlineStr">
         <is>
           <t>10 20 30
 1</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="S26" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="T26" t="inlineStr">
         <is>
           <t>1 2 3
 x</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="U26" t="inlineStr">
         <is>
           <t>Invalid index</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="V26" t="inlineStr">
         <is>
           <t>1 2 3
 9</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="W26" t="inlineStr">
         <is>
           <t>Out of range</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="X26" t="inlineStr">
         <is>
           <t>1 2 3
 0</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="Y26" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="Z26" t="inlineStr">
         <is>
           <t>1 2 3
 -1</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AA26" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AB26" t="inlineStr">
         <is>
           <t>5
 y</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AC26" t="inlineStr">
         <is>
           <t>Invalid index</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AD26" t="inlineStr">
         <is>
           <t>1 2 3 4
 3</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AE26" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AG6" t="inlineStr">
+      <c r="AG26" t="inlineStr">
         <is>
           <t>nums = input().split()
 raw = input()
 try:
     i = int(raw)
     print(nums[i])
-except ValueError:
+except ValueError:          # index text wasn't a valid integer
     print("Invalid index")
-except IndexError:
+except IndexError:          # index was a valid integer but out of range
     print("Out of range")</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>Python - Divide the List</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Read a line of numbers and a divisor. Print each number divided by the divisor (integer division), separated by spaces. If the divisor is zero, print 'Cannot divide' instead.
-### Input Format
-- Line 1: Space-separated numbers
-- Line 2: The divisor
-### Output Format
-```
-5 10 15
-```
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>A bill-splitting app divides a list of item costs evenly among a group of friends, but if someone accidentally sets the group size to zero, the division needs to be caught instead of crashing the app.
+Read a line of numbers and a divisor. Print each number divided by the divisor using integer division, separated by spaces. If the divisor is zero, print 'Cannot divide' instead.
 ### Example Walkthrough
 In the sample, the numbers are `10 20 30` and the divisor is `2`. Dividing each gives `5`, `10`, and `15`, so the program prints `5 10 15`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
         <v>5</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>exception-handling</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>try-except</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O7" t="b">
+      <c r="O27" t="b">
         <v>0</v>
       </c>
-      <c r="P7" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q7" t="b">
-        <v>1</v>
-      </c>
-      <c r="R7" t="inlineStr">
+      <c r="P27" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q27" t="b">
+        <v>1</v>
+      </c>
+      <c r="R27" t="inlineStr">
         <is>
           <t>10 20 30
 2</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="S27" t="inlineStr">
         <is>
           <t>5 10 15</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="T27" t="inlineStr">
         <is>
           <t>5 6
 0</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="U27" t="inlineStr">
         <is>
           <t>Cannot divide</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="V27" t="inlineStr">
         <is>
           <t>9
 3</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="W27" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="X27" t="inlineStr">
         <is>
           <t>0
 5</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="Y27" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="Z27" t="inlineStr">
         <is>
           <t>-10 -20
 2</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AA27" t="inlineStr">
         <is>
           <t>-5 -10</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AB27" t="inlineStr">
         <is>
           <t>1
 1</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AC27" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AD27" t="inlineStr">
         <is>
           <t>-9
 0</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AE27" t="inlineStr">
         <is>
           <t>Cannot divide</t>
         </is>
       </c>
-      <c r="AG7" t="inlineStr">
+      <c r="AG27" t="inlineStr">
         <is>
           <t>nums = list(map(int, input().split()))
 divisor = int(input())
 try:
     result = [n // divisor for n in nums]
     print(*result)
-except ZeroDivisionError:
+except ZeroDivisionError:   # divisor was zero
     print("Cannot divide")</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>Python - Safe Average</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Read N, then N numbers on separate lines, and print their average. If N is zero there is no data, so catch the division error and print 'No data'.
-### Input Format
-- Line 1: N
-- Next N lines: one number each
-### Output Format
-```
-20.0
-```
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>The same bill-splitting app also shows the average expense per participant for a trip, calculated by dividing the total by the number of participants entered so far, but if no participants have been added yet, that division has nothing to work with.
+Read N, then N numbers on separate lines, and print their average. If N is zero there is no data, so catch the division error and print 'No data'.
 ### Example Walkthrough
 In the sample, `N` is `3` with values `10`, `20`, and `30`. Their average is `20.0`, so the program prints `20.0`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
         <v>5</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>exception-handling</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>try-except</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O8" t="b">
+      <c r="O28" t="b">
         <v>0</v>
       </c>
-      <c r="P8" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q8" t="b">
-        <v>1</v>
-      </c>
-      <c r="R8" t="inlineStr">
+      <c r="P28" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q28" t="b">
+        <v>1</v>
+      </c>
+      <c r="R28" t="inlineStr">
         <is>
           <t>3
 10
@@ -5484,56 +4923,56 @@
 30</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="S28" t="inlineStr">
         <is>
           <t>20.0</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="T28" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="U28" t="inlineStr">
         <is>
           <t>No data</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="V28" t="inlineStr">
         <is>
           <t>1
 50</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="W28" t="inlineStr">
         <is>
           <t>50.0</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="X28" t="inlineStr">
         <is>
           <t>2
 -5
 5</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="Y28" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="Z28" t="inlineStr">
         <is>
           <t>1
 0</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AA28" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AB28" t="inlineStr">
         <is>
           <t>4
 1
@@ -5542,276 +4981,263 @@
 4</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AC28" t="inlineStr">
         <is>
           <t>2.5</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AD28" t="inlineStr">
         <is>
           <t>2
 100
 200</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AE28" t="inlineStr">
         <is>
           <t>150.0</t>
         </is>
       </c>
-      <c r="AG8" t="inlineStr">
+      <c r="AG28" t="inlineStr">
         <is>
           <t>n = int(input())
 nums = [int(input()) for _ in range(n)]
 try:
     print(sum(nums) / len(nums))
-except ZeroDivisionError:
+except ZeroDivisionError:   # no numbers to average when n is zero
     print("No data")</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>Python - Raise Age Error</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>A hospital registration form accepts a patient's age, but a negative age makes no sense, so the form manually raises an error when it sees one and reports the entry as invalid.
 Write a program that reads a whole number age inside a `try` block; if the age is negative, manually `raise ValueError()`. Catch that error and print `Invalid age`; otherwise print `Valid`.
-### Input Format
-- Line 1: Age
-### Output Format
-```
-Valid
-```
 ### Example Walkthrough
 In the sample, the age is 18, which is not negative, so no error is raised and the program prints `Valid`. An age of `-1` would raise the error and print `Invalid age` instead.
 ### Constraints
 - All numeric inputs are valid whole numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
         <v>5</v>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>exception-handling</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>raising-exceptions</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O9" t="b">
+      <c r="O29" t="b">
         <v>0</v>
       </c>
-      <c r="P9" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q9" t="b">
-        <v>1</v>
-      </c>
-      <c r="R9" t="inlineStr">
+      <c r="P29" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q29" t="b">
+        <v>1</v>
+      </c>
+      <c r="R29" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="S29" t="inlineStr">
         <is>
           <t>Valid</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="T29" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="U29" t="inlineStr">
         <is>
           <t>Invalid age</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="V29" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="W29" t="inlineStr">
         <is>
           <t>Valid</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="X29" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="Y29" t="inlineStr">
         <is>
           <t>Valid</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="Z29" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AA29" t="inlineStr">
         <is>
           <t>Valid</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AB29" t="inlineStr">
         <is>
           <t>-99</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AC29" t="inlineStr">
         <is>
           <t>Invalid age</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AD29" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AE29" t="inlineStr">
         <is>
           <t>Valid</t>
         </is>
       </c>
-      <c r="AG9" t="inlineStr">
+      <c r="AG29" t="inlineStr">
         <is>
           <t>try:
  age=int(input())
- if age&lt;0: raise ValueError()
+ if age&lt;0: raise ValueError()   # manually flag a negative age as invalid
  print("Valid")
 except ValueError: print("Invalid age")</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t>Python - Retry First Valid</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>A sensor-reading pipeline gets a batch of raw readings that sometimes include garbled, non-numeric entries; the software needs to skip over the bad readings and report the very first valid numeric reading it finds.
 Write a program that reads a whole number N, then reads N more lines one at a time, trying to convert each to an integer inside a `try` block; skip (using `except ValueError: pass`) any line that fails to convert, and print the first one that succeeds. If none of the N lines are valid numbers, print `None`.
-### Input Format
-- Line 1: N, the number of readings
-- Next N lines: raw readings, which may or may not be valid whole numbers
-### Output Format
-```
-5
-```
 ### Example Walkthrough
 In the sample, N is 3 with readings `a`, `5`, and `6`. The first reading `a` fails to convert and is skipped, the second reading `5` converts successfully, so the program prints `5` and stops checking further readings.
 ### Constraints
 - N is a valid whole number matching the number of lines that follow.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
         <v>5</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>exception-handling</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>defensive-programming</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O10" t="b">
+      <c r="O30" t="b">
         <v>0</v>
       </c>
-      <c r="P10" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q10" t="b">
-        <v>1</v>
-      </c>
-      <c r="R10" t="inlineStr">
+      <c r="P30" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q30" t="b">
+        <v>1</v>
+      </c>
+      <c r="R30" t="inlineStr">
         <is>
           <t>3
 a
@@ -5819,35 +5245,35 @@
 6</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="S30" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="T30" t="inlineStr">
         <is>
           <t>2
 x
 y</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="U30" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="V30" t="inlineStr">
         <is>
           <t>1
 10</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="W30" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="X30" t="inlineStr">
         <is>
           <t>4
 no
@@ -5856,22 +5282,22 @@
 9</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="Y30" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="Z30" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AA30" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AB30" t="inlineStr">
         <is>
           <t>3
 1
@@ -5879,471 +5305,272 @@
 3</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AC30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AD30" t="inlineStr">
         <is>
           <t>2
 blank
 7</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AE30" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AG10" t="inlineStr">
+      <c r="AG30" t="inlineStr">
         <is>
           <t>n=int(input()); found=False
 for _ in range(n):
  v=input()
  if not found:
-  try: print(int(v)); found=True
-  except ValueError: pass
+  try: print(int(v)); found=True   # stop after the first valid number
+  except ValueError: pass          # skip garbled, non-numeric readings
 if not found: print("None")</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>Python - Custom Low Balance</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>A banking app defines its own custom exception, `LowBalanceError`, to clearly signal when a withdrawal would exceed the account balance, rather than reusing a generic built-in exception for something this specific.
 Define a class `LowBalanceError` that inherits from `Exception`. Write a program that reads a balance and a withdrawal amount; if the withdrawal is greater than the balance, `raise LowBalanceError()`. Catch that error and print `Insufficient`; otherwise print `Balance` followed by the balance after the withdrawal.
-### Input Format
-- Line 1: Balance
-- Line 2: Withdrawal amount
-### Output Format
-```
-Balance 70.0
-```
 ### Example Walkthrough
 In the sample, the balance is 100 and the withdrawal is 30. Since 30 does not exceed 100, no error is raised, and the remaining balance is 100 - 30 = 70.0, so the program prints `Balance 70.0`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
         <v>5</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>exception-handling</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>custom-exceptions</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O11" t="b">
+      <c r="O31" t="b">
         <v>0</v>
       </c>
-      <c r="P11" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q11" t="b">
-        <v>1</v>
-      </c>
-      <c r="R11" t="inlineStr">
+      <c r="P31" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q31" t="b">
+        <v>1</v>
+      </c>
+      <c r="R31" t="inlineStr">
         <is>
           <t>100
 30</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="S31" t="inlineStr">
         <is>
           <t>Balance 70.0</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="T31" t="inlineStr">
         <is>
           <t>50
 60</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U31" t="inlineStr">
         <is>
           <t>Insufficient</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="V31" t="inlineStr">
         <is>
           <t>0
 0</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="W31" t="inlineStr">
         <is>
           <t>Balance 0.0</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="X31" t="inlineStr">
         <is>
           <t>10
 10</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="Y31" t="inlineStr">
         <is>
           <t>Balance 0.0</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="Z31" t="inlineStr">
         <is>
           <t>-5
 1</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AA31" t="inlineStr">
         <is>
           <t>Insufficient</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AB31" t="inlineStr">
         <is>
           <t>100.5
 0.5</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AC31" t="inlineStr">
         <is>
           <t>Balance 100.0</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AD31" t="inlineStr">
         <is>
           <t>5
 4</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
+      <c r="AE31" t="inlineStr">
         <is>
           <t>Balance 1.0</t>
         </is>
       </c>
-      <c r="AG11" t="inlineStr">
-        <is>
-          <t>class LowBalanceError(Exception): pass
+      <c r="AG31" t="inlineStr">
+        <is>
+          <t>class LowBalanceError(Exception): pass   # distinct type makes this failure easy to catch specifically
 try:
  b=float(input()); w=float(input())
- if w&gt;b: raise LowBalanceError()
+ if w&gt;b: raise LowBalanceError()   # signal that the withdrawal exceeds the balance
  print("Balance", b-w)
 except LowBalanceError: print("Insufficient")</t>
         </is>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AH11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>explanation</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>score</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>difficulty</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>bloomTaxonomy</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>tags</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>subjects</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>topics</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>subTopics</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>companies</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>codingType</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>language</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>supportAllLanguages</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>enablePartialScore</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>ignoreCase</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>testcase1_input</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>testcase1_output</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>testcase2_input</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>testcase2_output</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>testcase3_input</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>testcase3_output</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>testcase4_input</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>testcase4_output</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>testcase5_input</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>testcase5_output</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>testcase6_input</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>testcase6_output</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>testcase7_input</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>testcase7_output</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>preloadCode_python</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>solution_python</t>
-        </is>
-      </c>
-      <c r="AH1" t="inlineStr">
-        <is>
-          <t>hints</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="32">
+      <c r="A32" t="inlineStr">
         <is>
           <t>Python - Parse CSV Safely</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Read N lines, each meant to be 'name,age'. A line is valid only if it has exactly two fields, a non-empty name, and an age that is a whole number. Print the names from the valid lines, one per line.
-### Input Format
-- Line 1: N
-- Next N lines: records
-### Output Format
-```
-asha
-```
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>A spreadsheet importer reads student records line by line, each expected to be in the form 'name,age', but real-world exports often contain malformed rows: missing fields, blank names, or ages typed as text.
+Read N lines, each meant to be 'name,age'. A line is valid only if it has exactly two fields, a non-empty name, and an age that is a whole number. Print the names from the valid lines, one per line.
 ### Example Walkthrough
 In the sample, `N` is `2` with records `asha,20` and `kabir,x`. The first record is valid and prints `asha`; the second has a non-numeric age and is skipped.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
         <v>5</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>exception-handling</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>defensive-programming</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O2" t="b">
+      <c r="O32" t="b">
         <v>0</v>
       </c>
-      <c r="P2" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q2" t="b">
-        <v>1</v>
-      </c>
-      <c r="R2" t="inlineStr">
+      <c r="P32" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q32" t="b">
+        <v>1</v>
+      </c>
+      <c r="R32" t="inlineStr">
         <is>
           <t>3
 asha,20
@@ -6351,53 +5578,53 @@
 sam,x</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="S32" t="inlineStr">
         <is>
           <t>asha</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="T32" t="inlineStr">
         <is>
           <t>2
 a,10
 b,20</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="U32" t="inlineStr">
         <is>
           <t>a
 b</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="V32" t="inlineStr">
         <is>
           <t>2
 x,5
 ,7</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="W32" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="X32" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="Z32" t="inlineStr">
         <is>
           <t>1
 zed,1</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AA32" t="inlineStr">
         <is>
           <t>zed</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AB32" t="inlineStr">
         <is>
           <t>4
 a,1,2
@@ -6406,18 +5633,18 @@
 d,x</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AC32" t="inlineStr">
         <is>
           <t>b</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AD32" t="inlineStr">
         <is>
           <t>1
 ,10</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AG32" t="inlineStr">
         <is>
           <t>n = int(input())
 for _ in range(n):
@@ -6425,499 +5652,484 @@
     parts = line.split(",")
     try:
         if len(parts) != 2:
-            raise ValueError()
+            raise ValueError()      # wrong number of fields makes the line invalid
         name, age = parts
         if name == "":
-            raise ValueError()
-        int(age)
+            raise ValueError()      # empty name makes the line invalid
+        int(age)                    # confirms age is a whole number; raises ValueError if not
         print(name)
     except ValueError:
-        continue</t>
+        continue                    # skip this line and move to the next</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="33">
+      <c r="A33" t="inlineStr">
         <is>
           <t>Python - Password Strength</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Read a password. It must be at least 6 characters long and contain at least one digit. Print 'Strong' if both hold, 'Too short' if it is under 6 characters, or 'Needs a digit' if it has no digit.
-### Input Format
-- Line 1: A password
-### Output Format
-```
-Strong
-```
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>The account-creation page of a college's online exam portal enforces a minimum bar for passwords before letting a student proceed: at least 6 characters, with at least one digit mixed in.
+Read a password. It must be at least 6 characters long and contain at least one digit. Print 'Strong' if both conditions hold, 'Too short' if it is under 6 characters, or 'Needs a digit' if it has no digit.
 ### Example Walkthrough
 In the sample, the password is `abcdef1`. It has `7` characters (at least `6`) and contains a digit, so the program prints `Strong`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
         <v>5</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>exception-handling</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>custom-exceptions</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O3" t="b">
+      <c r="O33" t="b">
         <v>0</v>
       </c>
-      <c r="P3" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q3" t="b">
-        <v>1</v>
-      </c>
-      <c r="R3" t="inlineStr">
+      <c r="P33" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q33" t="b">
+        <v>1</v>
+      </c>
+      <c r="R33" t="inlineStr">
         <is>
           <t>abc123</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="S33" t="inlineStr">
         <is>
           <t>Strong</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="T33" t="inlineStr">
         <is>
           <t>ab1</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="U33" t="inlineStr">
         <is>
           <t>Too short</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="V33" t="inlineStr">
         <is>
           <t>abcdef</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="W33" t="inlineStr">
         <is>
           <t>Needs a digit</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="X33" t="inlineStr">
         <is>
           <t>123456</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Y33" t="inlineStr">
         <is>
           <t>Strong</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="Z33" t="inlineStr">
         <is>
           <t>abcde1</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AA33" t="inlineStr">
         <is>
           <t>Strong</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AB33" t="inlineStr">
         <is>
           <t xml:space="preserve">
 </t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AC33" t="inlineStr">
         <is>
           <t>Too short</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AD33" t="inlineStr">
         <is>
           <t>abc12345</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AE33" t="inlineStr">
         <is>
           <t>Strong</t>
         </is>
       </c>
-      <c r="AG3" t="inlineStr">
+      <c r="AG33" t="inlineStr">
         <is>
           <t>class WeakPassword(Exception):
-    pass
+    pass    # a distinct exception type makes this failure easy to catch specifically
 password = input()
 try:
     if len(password) &lt; 6:
-        raise WeakPassword("Too short")
+        raise WeakPassword("Too short")     # signal the specific reason it failed
     if not any(ch.isdigit() for ch in password):
         raise WeakPassword("Needs a digit")
     print("Strong")
 except WeakPassword as e:
-    print(e)</t>
+    print(e)                                 # print whichever reason was raised</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="34">
+      <c r="A34" t="inlineStr">
         <is>
           <t>Python - Safe JSON Parse</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Read one line and try to parse it as a JSON object. If it is not valid JSON, print 'Invalid JSON'. Otherwise print how many keys the object has.
-### Input Format
-- Line 1: A possible JSON object
-### Output Format
-```
-2
-```
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>A desktop app lets users import their settings from a JSON config file pasted in as text, but a corrupted or hand-edited file might not be valid JSON at all.
+Read one line and try to parse it as a JSON object. If it is not valid JSON, print 'Invalid JSON'. Otherwise print how many keys the object has.
 ### Example Walkthrough
 In the sample, the JSON is `{"a": 1, "b": 2}`. It parses successfully and has `2` keys, so the program prints `2`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
         <v>5</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>exception-handling</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>try-except</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O4" t="b">
+      <c r="O34" t="b">
         <v>0</v>
       </c>
-      <c r="P4" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q4" t="b">
-        <v>1</v>
-      </c>
-      <c r="R4" t="inlineStr">
+      <c r="P34" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q34" t="b">
+        <v>1</v>
+      </c>
+      <c r="R34" t="inlineStr">
         <is>
           <t>{"a": 1, "b": 2}</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="S34" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="T34" t="inlineStr">
         <is>
           <t>not json</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="U34" t="inlineStr">
         <is>
           <t>Invalid JSON</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="V34" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="W34" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="X34" t="inlineStr">
         <is>
           <t>{"single": 1}</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="Y34" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="Z34" t="inlineStr">
         <is>
           <t>[1,2,3]</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AA34" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AB34" t="inlineStr">
         <is>
           <t>{invalid</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AC34" t="inlineStr">
         <is>
           <t>Invalid JSON</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AD34" t="inlineStr">
         <is>
           <t>{"a":1,"b":2,"c":3}</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
+      <c r="AE34" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AG4" t="inlineStr">
+      <c r="AG34" t="inlineStr">
         <is>
           <t>import json
 line = input()
 try:
     data = json.loads(line)
     print(len(data))
-except json.JSONDecodeError:
+except json.JSONDecodeError:    # catches malformed JSON specifically, not all errors
     print("Invalid JSON")</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="35">
+      <c r="A35" t="inlineStr">
         <is>
           <t>Python - Grade with Validation</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Read a mark. If it is not between 0 and 100, print 'Invalid marks'. Otherwise print the grade: 'A' for 90 or more, 'B' for 75 or more, 'C' for 60 or more, and 'F' below that.
-### Input Format
-- Line 1: A mark
-### Output Format
-```
-A
-```
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>A report-card generator takes a student's mark for a subject and converts it into a letter grade, but marks entered by a teacher should always fall between 0 and 100.
+Read a mark. If it is not between 0 and 100, print 'Invalid marks'. Otherwise print the grade: 'A' for 90 or more, 'B' for 75 or more, 'C' for 60 or more, and 'F' below that.
 ### Example Walkthrough
 In the sample, the mark is `95`. Since `95` is at least `90`, the program prints `A`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
         <v>5</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>exception-handling</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t>raising-exceptions</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O5" t="b">
+      <c r="O35" t="b">
         <v>0</v>
       </c>
-      <c r="P5" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q5" t="b">
-        <v>1</v>
-      </c>
-      <c r="R5" t="inlineStr">
+      <c r="P35" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q35" t="b">
+        <v>1</v>
+      </c>
+      <c r="R35" t="inlineStr">
         <is>
           <t>95</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="S35" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="T35" t="inlineStr">
         <is>
           <t>150</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="U35" t="inlineStr">
         <is>
           <t>Invalid marks</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="V35" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="W35" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="X35" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="Y35" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="Z35" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AA35" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AB35" t="inlineStr">
         <is>
           <t>-5</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AC35" t="inlineStr">
         <is>
           <t>Invalid marks</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AD35" t="inlineStr">
         <is>
           <t>59</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
+      <c r="AE35" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="AG5" t="inlineStr">
+      <c r="AG35" t="inlineStr">
         <is>
           <t>marks = int(input())
 try:
     if not (0 &lt;= marks &lt;= 100):
-        raise ValueError()
+        raise ValueError()      # marks outside the valid range
     if marks &gt;= 90:
         print("A")
     elif marks &gt;= 75:
@@ -6931,87 +6143,81 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="36">
+      <c r="A36" t="inlineStr">
         <is>
           <t>Python - Batch Convert</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Read N values on separate lines and try to convert each to a whole number. Print 'ok X fail Y' with the counts of successful and failed conversions.
-### Input Format
-- Line 1: N
-- Next N lines: values
-### Output Format
-```
-ok 3 fail 1
-```
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>A batch unit-converter tool reads a list of measurements typed in by a user and tries to convert each one to a whole number before processing them, but some entries in the batch are typos.
+Read N values on separate lines and try to convert each to a whole number. Print 'ok X fail Y' with the counts of successful and failed conversions.
 ### Example Walkthrough
 In the sample, `N` is `4` with values `1`, `2`, `x`, and `3`. Three convert successfully and one fails, so the program prints `ok 3 fail 1`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
         <v>5</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>exception-handling</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K36" t="inlineStr">
         <is>
           <t>exception-handling-patterns</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="N36" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O6" t="b">
+      <c r="O36" t="b">
         <v>0</v>
       </c>
-      <c r="P6" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q6" t="b">
-        <v>1</v>
-      </c>
-      <c r="R6" t="inlineStr">
+      <c r="P36" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q36" t="b">
+        <v>1</v>
+      </c>
+      <c r="R36" t="inlineStr">
         <is>
           <t>4
 1
@@ -7020,56 +6226,56 @@
 3</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="S36" t="inlineStr">
         <is>
           <t>ok 3 fail 1</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="T36" t="inlineStr">
         <is>
           <t>2
 a
 b</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="U36" t="inlineStr">
         <is>
           <t>ok 0 fail 2</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="V36" t="inlineStr">
         <is>
           <t>1
 5</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="W36" t="inlineStr">
         <is>
           <t>ok 1 fail 0</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="X36" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="Y36" t="inlineStr">
         <is>
           <t>ok 0 fail 0</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="Z36" t="inlineStr">
         <is>
           <t>1
 0</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AA36" t="inlineStr">
         <is>
           <t>ok 1 fail 0</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AB36" t="inlineStr">
         <is>
           <t>3
 -1
@@ -7077,12 +6283,12 @@
 -3</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AC36" t="inlineStr">
         <is>
           <t>ok 3 fail 0</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AD36" t="inlineStr">
         <is>
           <t>5
 1
@@ -7092,12 +6298,12 @@
 5</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AE36" t="inlineStr">
         <is>
           <t>ok 5 fail 0</t>
         </is>
       </c>
-      <c r="AG6" t="inlineStr">
+      <c r="AG36" t="inlineStr">
         <is>
           <t>n = int(input())
 ok = fail = 0
@@ -7106,95 +6312,86 @@
         int(input())
         ok += 1
     except ValueError:
-        fail += 1
+        fail += 1            # count invalid entries instead of crashing
 print(f"ok {ok} fail {fail}")</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="37">
+      <c r="A37" t="inlineStr">
         <is>
           <t>Python - Safe Matrix Access</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Read a grid with R rows and C columns, then Q queries, each a row and column. For each query print the value at that position, or 'Out of bounds' if the position is outside the grid.
-### Input Format
-- Line 1: R and C
-- Next R lines: grid rows
-- Then: Q
-- Next Q lines: 'row col'
-### Output Format
-```
-2
-Out of bounds
-```
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>A classroom seating-chart app stores students in a grid of rows and columns, and a teacher can query any seat by row and column to see who sits there, but some queries might point outside the actual grid.
+Read a grid with R rows and C columns, then Q queries, each a row and column. For each query, print the value at that position, or 'Out of bounds' if the position is outside the grid.
 ### Example Walkthrough
 In the sample, the grid is `2` by `2`: `1 2` and `3 4`, with `2` queries. The first query `0 1` reads the grid position and prints `2`; the second query `5 5` falls outside the grid, so the program prints `Out of bounds`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
         <v>5</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>exception-handling</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K37" t="inlineStr">
         <is>
           <t>exception-handling-patterns</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="N37" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O7" t="b">
+      <c r="O37" t="b">
         <v>0</v>
       </c>
-      <c r="P7" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q7" t="b">
-        <v>1</v>
-      </c>
-      <c r="R7" t="inlineStr">
+      <c r="P37" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q37" t="b">
+        <v>1</v>
+      </c>
+      <c r="R37" t="inlineStr">
         <is>
           <t>2 2
 1 2
@@ -7204,13 +6401,13 @@
 5 5</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="S37" t="inlineStr">
         <is>
           <t>2
 Out of bounds</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="T37" t="inlineStr">
         <is>
           <t>1 1
 9
@@ -7218,12 +6415,12 @@
 0 0</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="U37" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="V37" t="inlineStr">
         <is>
           <t>2 2
 1 2
@@ -7232,12 +6429,12 @@
 1 1</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="W37" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="X37" t="inlineStr">
         <is>
           <t>1 1
 5
@@ -7245,19 +6442,19 @@
 -1 0</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="Y37" t="inlineStr">
         <is>
           <t>Out of bounds</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="Z37" t="inlineStr">
         <is>
           <t>1 1
 5
 0</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AB37" t="inlineStr">
         <is>
           <t>3 3
 1 2 3
@@ -7268,13 +6465,13 @@
 0 0</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AC37" t="inlineStr">
         <is>
           <t>9
 1</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AD37" t="inlineStr">
         <is>
           <t>2 2
 1 2
@@ -7283,12 +6480,12 @@
 10 10</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AE37" t="inlineStr">
         <is>
           <t>Out of bounds</t>
         </is>
       </c>
-      <c r="AG7" t="inlineStr">
+      <c r="AG37" t="inlineStr">
         <is>
           <t>r, c = map(int, input().split())
 grid = [list(map(int, input().split())) for _ in range(r)]
@@ -7297,421 +6494,401 @@
     row, col = map(int, input().split())
     try:
         if row &lt; 0 or col &lt; 0:
-            raise IndexError()
+            raise IndexError()   # negative indices are out of bounds too
         print(grid[row][col])
-    except IndexError:
+    except IndexError:           # catches both the manual raise and Python's own out-of-range error
         print("Out of bounds")</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t>Python - Robust Statistics</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Read a line of tokens. Compute the average of the ones that are valid numbers, printed to 1 decimal place. If none of the tokens are valid numbers, print 'No valid data'.
-### Input Format
-- Line 1: Space-separated tokens
-### Output Format
-```
-20.0
-```
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>A class-analytics dashboard computes the average of a batch of test scores pulled from a shared spreadsheet, but some cells contain stray text instead of a score, and if the whole batch turns out to have no usable numbers, there's nothing to average.
+Read a line of tokens. Compute the average of the ones that are valid numbers, printed to 1 decimal place. If none of the tokens are valid numbers, print 'No valid data'.
 ### Example Walkthrough
 In the sample, the tokens are `10 x 20 y 30`. Only `10`, `20`, and `30` are valid numbers, and their average is `20.0`, so the program prints `20.0`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
         <v>5</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t>exception-handling</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K38" t="inlineStr">
         <is>
           <t>defensive-programming</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="N38" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O8" t="b">
+      <c r="O38" t="b">
         <v>0</v>
       </c>
-      <c r="P8" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q8" t="b">
-        <v>1</v>
-      </c>
-      <c r="R8" t="inlineStr">
+      <c r="P38" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q38" t="b">
+        <v>1</v>
+      </c>
+      <c r="R38" t="inlineStr">
         <is>
           <t>10 20 x 30</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="S38" t="inlineStr">
         <is>
           <t>20.0</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="T38" t="inlineStr">
         <is>
           <t>a b c</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="U38" t="inlineStr">
         <is>
           <t>No valid data</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="V38" t="inlineStr">
         <is>
           <t>5 5</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="W38" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="X38" t="inlineStr">
         <is>
           <t>0 0</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="Y38" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="Z38" t="inlineStr">
         <is>
           <t>-5 5 -10</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AA38" t="inlineStr">
         <is>
           <t>-3.3</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AB38" t="inlineStr">
         <is>
           <t>1 2 3 4 5</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AC38" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AD38" t="inlineStr">
         <is>
           <t>x y 10</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AE38" t="inlineStr">
         <is>
           <t>10.0</t>
         </is>
       </c>
-      <c r="AG8" t="inlineStr">
+      <c r="AG38" t="inlineStr">
         <is>
           <t>numbers = []
 for token in input().split():
     try:
         numbers.append(int(token))
     except ValueError:
-        pass
+        pass                     # skip tokens that aren't valid numbers
 try:
     print(round(sum(numbers) / len(numbers), 1))
-except ZeroDivisionError:
+except ZeroDivisionError:        # no valid numbers were collected
     print("No valid data")</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="39">
+      <c r="A39" t="inlineStr">
         <is>
           <t>Python - Parse Marks Safely</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>A results-upload tool receives a row of marks typed by a teacher, but sometimes a cell contains a stray letter instead of a number; the tool should skip just the bad entries and still compute the average of the valid marks.
 Write a program that reads a line of space-separated values, tries to convert each one to an integer inside a `try` block (skipping any that raise `ValueError`), and prints the average of the values that converted successfully. If none of them are valid numbers, print `No valid marks`.
-### Input Format
-- Line 1: Space-separated values, which may or may not all be valid whole numbers
-### Output Format
-```
-15.0
-```
 ### Example Walkthrough
 In the sample, the values are `10 20 x`. `10` and `20` convert successfully but `x` does not and is skipped, so the average of the valid marks is (10 + 20) / 2 = 15.0, which the program prints.
 ### Constraints
 - The input line has at least one value.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
         <v>5</v>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t>exception-handling</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K39" t="inlineStr">
         <is>
           <t>defensive-programming</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="N39" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O9" t="b">
+      <c r="O39" t="b">
         <v>0</v>
       </c>
-      <c r="P9" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q9" t="b">
-        <v>1</v>
-      </c>
-      <c r="R9" t="inlineStr">
+      <c r="P39" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q39" t="b">
+        <v>1</v>
+      </c>
+      <c r="R39" t="inlineStr">
         <is>
           <t>10 20 x</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="S39" t="inlineStr">
         <is>
           <t>15.0</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="T39" t="inlineStr">
         <is>
           <t>a b</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="U39" t="inlineStr">
         <is>
           <t>No valid marks</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="V39" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="W39" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="X39" t="inlineStr">
         <is>
           <t>-5 5</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="Y39" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="Z39" t="inlineStr">
         <is>
           <t>1 2 3</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AA39" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AB39" t="inlineStr">
         <is>
           <t>0 x 0</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AC39" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AD39" t="inlineStr">
         <is>
           <t>3.5 4</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AE39" t="inlineStr">
         <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="AG9" t="inlineStr">
+      <c r="AG39" t="inlineStr">
         <is>
           <t>marks=[]
 for v in input().split():
  try: marks.append(int(v))
- except ValueError: pass
+ except ValueError: pass         # skip stray non-numeric entries
 print(sum(marks)/len(marks) if marks else "No valid marks")</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="40">
+      <c r="A40" t="inlineStr">
         <is>
           <t>Python - Nested Safe Access</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>A seating-chart app looks up whether a specific seat, given as a row and column number, is occupied in a grid stored as a list of lists, and must handle both coordinates that are out of range and inputs that aren't numbers at all.
 Write a program that reads a whole number `rows`, then reads `rows` lines each with space-separated values to build a grid (a list of lists), then reads a row index and a column index, and prints the value at that position. If either index is not a valid whole number, or is out of range, catch the error and print `Error`.
-### Input Format
-- Line 1: Number of rows
-- Next `rows` lines: space-separated values for that row
-- Next line: row index to look up
-- Final line: column index to look up
-### Output Format
-```
-2
-```
 ### Example Walkthrough
 In the sample, the grid has 2 rows, `1 2` and `3 4`, and the lookup is row `0`, column `1`. The value at row 0, column 1 is `2`, so the program prints `2`.
 ### Constraints
 - All numeric inputs are valid whole numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
         <v>5</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>exception-handling</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="K40" t="inlineStr">
         <is>
           <t>exception-handling-patterns</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="N40" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O10" t="b">
+      <c r="O40" t="b">
         <v>0</v>
       </c>
-      <c r="P10" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q10" t="b">
-        <v>1</v>
-      </c>
-      <c r="R10" t="inlineStr">
+      <c r="P40" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q40" t="b">
+        <v>1</v>
+      </c>
+      <c r="R40" t="inlineStr">
         <is>
           <t>2
 1 2
@@ -7720,12 +6897,12 @@
 1</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="S40" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="T40" t="inlineStr">
         <is>
           <t>1
 5
@@ -7733,12 +6910,12 @@
 0</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="U40" t="inlineStr">
         <is>
           <t>Error</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="V40" t="inlineStr">
         <is>
           <t>2
 1
@@ -7747,24 +6924,24 @@
 5</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="W40" t="inlineStr">
         <is>
           <t>Error</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="X40" t="inlineStr">
         <is>
           <t>0
 0
 0</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="Y40" t="inlineStr">
         <is>
           <t>Error</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="Z40" t="inlineStr">
         <is>
           <t>2
 1 2
@@ -7773,12 +6950,12 @@
 0</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AA40" t="inlineStr">
         <is>
           <t>Error</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AB40" t="inlineStr">
         <is>
           <t>2
 1 2
@@ -7787,12 +6964,12 @@
 0</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AC40" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AD40" t="inlineStr">
         <is>
           <t>1
 9
@@ -7800,176 +6977,170 @@
 0</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AE40" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="AG10" t="inlineStr">
+      <c r="AG40" t="inlineStr">
         <is>
           <t>rows=int(input()); m=[]
 for _ in range(rows): m.append(input().split())
 try: print(m[int(input())][int(input())])
-except (ValueError,IndexError): print("Error")</t>
+except (ValueError,IndexError): print("Error")   # catches bad index text or out-of-range coordinates</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="41">
+      <c r="A41" t="inlineStr">
         <is>
           <t>Python - Validate Password</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>A signup form checks whether a new password is strong enough (at least 6 characters long and containing at least one digit), manually raising an error internally for either failing condition and catching it to report the password as weak.
 Write a program that reads a password inside a `try` block; if it is shorter than 6 characters, or contains no digits, `raise ValueError()`. Catch that error and print `Weak`; otherwise print `Strong`.
-### Input Format
-- Line 1: A password
-### Output Format
-```
-Strong
-```
 ### Example Walkthrough
 In the sample, the password is `abc123`. It has 6 characters and contains digits, so neither condition raises an error, and the program prints `Strong`. A password like `abcdef` (no digits) would print `Weak` instead.
 ### Constraints
 - The input is a valid line of text with no leading or trailing spaces.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
         <v>5</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>exception-handling</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K41" t="inlineStr">
         <is>
           <t>raising-exceptions</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="N41" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O11" t="b">
+      <c r="O41" t="b">
         <v>0</v>
       </c>
-      <c r="P11" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q11" t="b">
-        <v>1</v>
-      </c>
-      <c r="R11" t="inlineStr">
+      <c r="P41" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q41" t="b">
+        <v>1</v>
+      </c>
+      <c r="R41" t="inlineStr">
         <is>
           <t>abc123</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="S41" t="inlineStr">
         <is>
           <t>Strong</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="T41" t="inlineStr">
         <is>
           <t>abcdef</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U41" t="inlineStr">
         <is>
           <t>Weak</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="V41" t="inlineStr">
         <is>
           <t>a1</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="W41" t="inlineStr">
         <is>
           <t>Weak</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="X41" t="inlineStr">
         <is>
           <t>password1</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="Y41" t="inlineStr">
         <is>
           <t>Strong</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="Z41" t="inlineStr">
         <is>
           <t>123456</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AA41" t="inlineStr">
         <is>
           <t>Strong</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AB41" t="inlineStr">
         <is>
           <t>ABCDEF1</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AC41" t="inlineStr">
         <is>
           <t>Strong</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AD41" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
+      <c r="AE41" t="inlineStr">
         <is>
           <t>Weak</t>
         </is>
       </c>
-      <c r="AG11" t="inlineStr">
+      <c r="AG41" t="inlineStr">
         <is>
           <t>try:
  p=input()
- if len(p)&lt;6: raise ValueError()
- if not any(ch.isdigit() for ch in p): raise ValueError()
+ if len(p)&lt;6: raise ValueError()          # too short fails the length check
+ if not any(ch.isdigit() for ch in p): raise ValueError()   # missing a digit also fails
  print("Strong")
 except ValueError: print("Weak")</t>
         </is>
